--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>131883760</v>
       </c>
       <c r="B11" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>131883788</v>
       </c>
       <c r="B12" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131883780</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131883767</v>
+        <v>131882924</v>
       </c>
       <c r="B14" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,42 +2051,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437078</v>
+        <v>436780</v>
       </c>
       <c r="R14" t="n">
-        <v>7010278</v>
+        <v>7010451</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2113,19 +2108,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131882924</v>
+        <v>131883767</v>
       </c>
       <c r="B15" t="n">
-        <v>91889</v>
+        <v>57948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,37 +2148,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436780</v>
+        <v>437078</v>
       </c>
       <c r="R15" t="n">
-        <v>7010451</v>
+        <v>7010278</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2220,9 +2210,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131883777</v>
+        <v>131883755</v>
       </c>
       <c r="B16" t="n">
-        <v>79315</v>
+        <v>78340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437160</v>
+        <v>436954</v>
       </c>
       <c r="R16" t="n">
-        <v>7010163</v>
+        <v>7010327</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131883782</v>
+        <v>131883777</v>
       </c>
       <c r="B17" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436983</v>
+        <v>437160</v>
       </c>
       <c r="R17" t="n">
-        <v>7010313</v>
+        <v>7010163</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131883759</v>
+        <v>131883782</v>
       </c>
       <c r="B18" t="n">
-        <v>83295</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436787</v>
+        <v>436983</v>
       </c>
       <c r="R18" t="n">
-        <v>7010440</v>
+        <v>7010313</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131883755</v>
+        <v>131883759</v>
       </c>
       <c r="B19" t="n">
-        <v>78338</v>
+        <v>83297</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436954</v>
+        <v>436787</v>
       </c>
       <c r="R19" t="n">
-        <v>7010327</v>
+        <v>7010440</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2792,7 +2792,7 @@
         <v>131883786</v>
       </c>
       <c r="B21" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131883769</v>
+        <v>131882928</v>
       </c>
       <c r="B22" t="n">
-        <v>57136</v>
+        <v>97963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,42 +2907,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437337</v>
+        <v>437191</v>
       </c>
       <c r="R22" t="n">
-        <v>7010352</v>
+        <v>7010182</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,19 +2964,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131882928</v>
+        <v>131883769</v>
       </c>
       <c r="B23" t="n">
-        <v>97960</v>
+        <v>57136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,37 +3004,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437191</v>
+        <v>437337</v>
       </c>
       <c r="R23" t="n">
-        <v>7010182</v>
+        <v>7010352</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3076,9 +3066,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,7 +3108,7 @@
         <v>131883761</v>
       </c>
       <c r="B24" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>131883789</v>
       </c>
       <c r="B25" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>131883775</v>
       </c>
       <c r="B26" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>131883776</v>
       </c>
       <c r="B27" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>131882931</v>
       </c>
       <c r="B28" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>131883784</v>
       </c>
       <c r="B29" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131883787</v>
+        <v>131882927</v>
       </c>
       <c r="B31" t="n">
-        <v>79315</v>
+        <v>92191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,37 +3860,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436824</v>
+        <v>437098</v>
       </c>
       <c r="R31" t="n">
-        <v>7010448</v>
+        <v>7010473</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3917,19 +3917,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3956,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131883778</v>
+        <v>131882917</v>
       </c>
       <c r="B32" t="n">
-        <v>79315</v>
+        <v>78340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,37 +3957,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437111</v>
+        <v>437024</v>
       </c>
       <c r="R32" t="n">
-        <v>7010195</v>
+        <v>7010309</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4024,19 +4014,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4063,10 +4043,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131882927</v>
+        <v>131883787</v>
       </c>
       <c r="B33" t="n">
-        <v>92188</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,37 +4054,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437098</v>
+        <v>436824</v>
       </c>
       <c r="R33" t="n">
-        <v>7010473</v>
+        <v>7010448</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4131,9 +4111,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,10 +4150,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131882917</v>
+        <v>131883778</v>
       </c>
       <c r="B34" t="n">
-        <v>78338</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4171,37 +4161,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437024</v>
+        <v>437111</v>
       </c>
       <c r="R34" t="n">
-        <v>7010309</v>
+        <v>7010195</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,9 +4218,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,7 +4260,7 @@
         <v>131883781</v>
       </c>
       <c r="B35" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>131883758</v>
       </c>
       <c r="B36" t="n">
-        <v>78338</v>
+        <v>78340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>131883785</v>
       </c>
       <c r="B37" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131883756</v>
+        <v>131883768</v>
       </c>
       <c r="B38" t="n">
-        <v>78338</v>
+        <v>57948</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4589,34 +4589,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436785</v>
+        <v>437044</v>
       </c>
       <c r="R38" t="n">
-        <v>7010497</v>
+        <v>7010321</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4648,7 +4653,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4658,7 +4663,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4685,32 +4690,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131882919</v>
+        <v>131882926</v>
       </c>
       <c r="B39" t="n">
-        <v>83295</v>
+        <v>92352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4720,10 +4725,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436779</v>
+        <v>437234</v>
       </c>
       <c r="R39" t="n">
-        <v>7010478</v>
+        <v>7010154</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4782,10 +4787,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131883779</v>
+        <v>131883756</v>
       </c>
       <c r="B40" t="n">
-        <v>79315</v>
+        <v>78340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4793,21 +4798,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4817,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437081</v>
+        <v>436785</v>
       </c>
       <c r="R40" t="n">
-        <v>7010232</v>
+        <v>7010497</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4852,7 +4857,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4862,7 +4867,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4889,32 +4894,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131882926</v>
+        <v>131882919</v>
       </c>
       <c r="B41" t="n">
-        <v>92349</v>
+        <v>83297</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4924,10 +4929,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437234</v>
+        <v>436779</v>
       </c>
       <c r="R41" t="n">
-        <v>7010154</v>
+        <v>7010478</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4986,10 +4991,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131883768</v>
+        <v>131883779</v>
       </c>
       <c r="B42" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,39 +5002,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437044</v>
+        <v>437081</v>
       </c>
       <c r="R42" t="n">
-        <v>7010321</v>
+        <v>7010232</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5101,7 +5101,7 @@
         <v>131882932</v>
       </c>
       <c r="B43" t="n">
-        <v>83287</v>
+        <v>83289</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>131883774</v>
       </c>
       <c r="B44" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>131882923</v>
       </c>
       <c r="B45" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>131882920</v>
       </c>
       <c r="B46" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131882930</v>
+        <v>131883773</v>
       </c>
       <c r="B47" t="n">
-        <v>79315</v>
+        <v>92191</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437227</v>
+        <v>436865</v>
       </c>
       <c r="R47" t="n">
-        <v>7010158</v>
+        <v>7010395</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5564,9 +5564,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5593,10 +5603,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131883773</v>
+        <v>131883762</v>
       </c>
       <c r="B48" t="n">
-        <v>92188</v>
+        <v>91892</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,21 +5614,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5628,10 +5638,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436865</v>
+        <v>436892</v>
       </c>
       <c r="R48" t="n">
-        <v>7010395</v>
+        <v>7010367</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5663,7 +5673,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5673,7 +5683,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5700,10 +5710,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131883762</v>
+        <v>131882930</v>
       </c>
       <c r="B49" t="n">
-        <v>91889</v>
+        <v>79317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5711,37 +5721,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436892</v>
+        <v>437227</v>
       </c>
       <c r="R49" t="n">
-        <v>7010367</v>
+        <v>7010158</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5768,19 +5778,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5807,10 +5807,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131882921</v>
+        <v>131882925</v>
       </c>
       <c r="B50" t="n">
-        <v>79905</v>
+        <v>57948</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5818,34 +5818,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437362</v>
+        <v>437206</v>
       </c>
       <c r="R50" t="n">
-        <v>7010336</v>
+        <v>7010436</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5904,10 +5912,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131883764</v>
+        <v>131882921</v>
       </c>
       <c r="B51" t="n">
-        <v>91889</v>
+        <v>79907</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5915,37 +5923,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436864</v>
+        <v>437362</v>
       </c>
       <c r="R51" t="n">
-        <v>7010391</v>
+        <v>7010336</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5972,19 +5980,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6011,10 +6009,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131882925</v>
+        <v>131883764</v>
       </c>
       <c r="B52" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,45 +6020,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437206</v>
+        <v>436864</v>
       </c>
       <c r="R52" t="n">
-        <v>7010436</v>
+        <v>7010391</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6087,9 +6077,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6119,7 +6119,7 @@
         <v>131882929</v>
       </c>
       <c r="B53" t="n">
-        <v>92261</v>
+        <v>92264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>131882922</v>
       </c>
       <c r="B54" t="n">
-        <v>92261</v>
+        <v>92264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>132341092</v>
       </c>
       <c r="B55" t="n">
-        <v>92617</v>
+        <v>92620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>132341099</v>
       </c>
       <c r="B58" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7424,32 +7424,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132340934</v>
+        <v>132341017</v>
       </c>
       <c r="B66" t="n">
-        <v>91852</v>
+        <v>57948</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437567</v>
+        <v>436985</v>
       </c>
       <c r="R66" t="n">
-        <v>7010358</v>
+        <v>7010332</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,6 +7495,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7521,7 +7526,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341017</v>
+        <v>132341012</v>
       </c>
       <c r="B67" t="n">
         <v>57948</v>
@@ -7556,10 +7561,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436985</v>
+        <v>436992</v>
       </c>
       <c r="R67" t="n">
-        <v>7010332</v>
+        <v>7010454</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7596,7 +7601,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7623,32 +7628,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341012</v>
+        <v>132340934</v>
       </c>
       <c r="B68" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7658,10 +7663,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436992</v>
+        <v>437567</v>
       </c>
       <c r="R68" t="n">
-        <v>7010454</v>
+        <v>7010358</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7694,11 +7699,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7932,7 +7932,7 @@
         <v>132340950</v>
       </c>
       <c r="B71" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341123</v>
+        <v>132341000</v>
       </c>
       <c r="B74" t="n">
-        <v>91885</v>
+        <v>57948</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436761</v>
+        <v>437046</v>
       </c>
       <c r="R74" t="n">
-        <v>7010448</v>
+        <v>7010396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,6 +8332,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8358,10 +8363,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341124</v>
+        <v>132341002</v>
       </c>
       <c r="B75" t="n">
-        <v>91885</v>
+        <v>57948</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8369,21 +8374,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8393,10 +8398,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436893</v>
+        <v>437060</v>
       </c>
       <c r="R75" t="n">
-        <v>7010302</v>
+        <v>7010387</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,6 +8434,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8455,10 +8465,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341000</v>
+        <v>132341123</v>
       </c>
       <c r="B76" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8466,21 +8476,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8490,10 +8500,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437046</v>
+        <v>436761</v>
       </c>
       <c r="R76" t="n">
-        <v>7010396</v>
+        <v>7010448</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8526,11 +8536,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8557,10 +8562,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341002</v>
+        <v>132341124</v>
       </c>
       <c r="B77" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8568,21 +8573,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8592,10 +8597,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437060</v>
+        <v>436893</v>
       </c>
       <c r="R77" t="n">
-        <v>7010387</v>
+        <v>7010302</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8628,11 +8633,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8659,7 +8659,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341015</v>
+        <v>132341021</v>
       </c>
       <c r="B78" t="n">
         <v>57948</v>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436933</v>
+        <v>437255</v>
       </c>
       <c r="R78" t="n">
-        <v>7010291</v>
+        <v>7010456</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8761,7 +8761,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341021</v>
+        <v>132341015</v>
       </c>
       <c r="B79" t="n">
         <v>57948</v>
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437255</v>
+        <v>436933</v>
       </c>
       <c r="R79" t="n">
-        <v>7010456</v>
+        <v>7010291</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8863,10 +8863,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341122</v>
+        <v>132341001</v>
       </c>
       <c r="B80" t="n">
-        <v>91885</v>
+        <v>57948</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8874,21 +8874,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436784</v>
+        <v>437047</v>
       </c>
       <c r="R80" t="n">
-        <v>7010502</v>
+        <v>7010396</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8934,6 +8934,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8960,7 +8965,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341001</v>
+        <v>132341011</v>
       </c>
       <c r="B81" t="n">
         <v>57948</v>
@@ -8995,10 +9000,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437047</v>
+        <v>437059</v>
       </c>
       <c r="R81" t="n">
-        <v>7010396</v>
+        <v>7010469</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9062,10 +9067,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341011</v>
+        <v>132341122</v>
       </c>
       <c r="B82" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9073,21 +9078,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9097,10 +9102,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437059</v>
+        <v>436784</v>
       </c>
       <c r="R82" t="n">
-        <v>7010469</v>
+        <v>7010502</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9133,11 +9138,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9473,7 +9473,7 @@
         <v>132341098</v>
       </c>
       <c r="B86" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -3849,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131882927</v>
+        <v>131883787</v>
       </c>
       <c r="B31" t="n">
-        <v>92191</v>
+        <v>79317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,37 +3860,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437098</v>
+        <v>436824</v>
       </c>
       <c r="R31" t="n">
-        <v>7010473</v>
+        <v>7010448</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3917,9 +3917,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,10 +3956,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131882917</v>
+        <v>131883778</v>
       </c>
       <c r="B32" t="n">
-        <v>78340</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,37 +3967,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437024</v>
+        <v>437111</v>
       </c>
       <c r="R32" t="n">
-        <v>7010309</v>
+        <v>7010195</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4014,9 +4024,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4043,10 +4063,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131883787</v>
+        <v>131882927</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>92191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4054,37 +4074,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436824</v>
+        <v>437098</v>
       </c>
       <c r="R33" t="n">
-        <v>7010448</v>
+        <v>7010473</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4111,19 +4131,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4150,10 +4160,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131883778</v>
+        <v>131882917</v>
       </c>
       <c r="B34" t="n">
-        <v>79317</v>
+        <v>78340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4161,37 +4171,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437111</v>
+        <v>437024</v>
       </c>
       <c r="R34" t="n">
-        <v>7010195</v>
+        <v>7010309</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4218,19 +4228,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,53 +4578,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131883768</v>
+        <v>131882926</v>
       </c>
       <c r="B38" t="n">
-        <v>57948</v>
+        <v>92352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437044</v>
+        <v>437234</v>
       </c>
       <c r="R38" t="n">
-        <v>7010321</v>
+        <v>7010154</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4651,19 +4646,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4690,48 +4675,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131882926</v>
+        <v>131883756</v>
       </c>
       <c r="B39" t="n">
-        <v>92352</v>
+        <v>78340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437234</v>
+        <v>436785</v>
       </c>
       <c r="R39" t="n">
-        <v>7010154</v>
+        <v>7010497</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4758,9 +4743,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4787,10 +4782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131883756</v>
+        <v>131882919</v>
       </c>
       <c r="B40" t="n">
-        <v>78340</v>
+        <v>83297</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4798,37 +4793,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436785</v>
+        <v>436779</v>
       </c>
       <c r="R40" t="n">
-        <v>7010497</v>
+        <v>7010478</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,19 +4850,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4894,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131882919</v>
+        <v>131883779</v>
       </c>
       <c r="B41" t="n">
-        <v>83297</v>
+        <v>79317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,37 +4890,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436779</v>
+        <v>437081</v>
       </c>
       <c r="R41" t="n">
-        <v>7010478</v>
+        <v>7010232</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4962,9 +4947,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,10 +4986,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131883779</v>
+        <v>131883768</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5002,34 +4997,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437081</v>
+        <v>437044</v>
       </c>
       <c r="R42" t="n">
-        <v>7010232</v>
+        <v>7010321</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -9470,10 +9470,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341098</v>
+        <v>132341016</v>
       </c>
       <c r="B86" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437162</v>
+        <v>436980</v>
       </c>
       <c r="R86" t="n">
-        <v>7010098</v>
+        <v>7010332</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9541,6 +9541,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9567,7 +9572,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341016</v>
+        <v>132341010</v>
       </c>
       <c r="B87" t="n">
         <v>57948</v>
@@ -9602,10 +9607,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436980</v>
+        <v>437123</v>
       </c>
       <c r="R87" t="n">
-        <v>7010332</v>
+        <v>7010418</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9642,7 +9647,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9669,7 +9674,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341010</v>
+        <v>132341019</v>
       </c>
       <c r="B88" t="n">
         <v>57948</v>
@@ -9704,10 +9709,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437123</v>
+        <v>437276</v>
       </c>
       <c r="R88" t="n">
-        <v>7010418</v>
+        <v>7010164</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9744,7 +9749,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9771,10 +9776,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341019</v>
+        <v>132341098</v>
       </c>
       <c r="B89" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,21 +9787,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9806,10 +9811,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437276</v>
+        <v>437162</v>
       </c>
       <c r="R89" t="n">
-        <v>7010164</v>
+        <v>7010098</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9842,11 +9847,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -7725,7 +7725,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341009</v>
+        <v>132341008</v>
       </c>
       <c r="B69" t="n">
         <v>57948</v>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437127</v>
+        <v>437222</v>
       </c>
       <c r="R69" t="n">
-        <v>7010372</v>
+        <v>7010260</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7827,7 +7827,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132341008</v>
+        <v>132341009</v>
       </c>
       <c r="B70" t="n">
         <v>57948</v>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437222</v>
+        <v>437127</v>
       </c>
       <c r="R70" t="n">
-        <v>7010260</v>
+        <v>7010372</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8863,10 +8863,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341001</v>
+        <v>132341122</v>
       </c>
       <c r="B80" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8874,21 +8874,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437047</v>
+        <v>436784</v>
       </c>
       <c r="R80" t="n">
-        <v>7010396</v>
+        <v>7010502</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8934,11 +8934,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8965,7 +8960,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341011</v>
+        <v>132341001</v>
       </c>
       <c r="B81" t="n">
         <v>57948</v>
@@ -9000,10 +8995,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437059</v>
+        <v>437047</v>
       </c>
       <c r="R81" t="n">
-        <v>7010469</v>
+        <v>7010396</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9067,10 +9062,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341122</v>
+        <v>132341011</v>
       </c>
       <c r="B82" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9078,21 +9073,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9102,10 +9097,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436784</v>
+        <v>437059</v>
       </c>
       <c r="R82" t="n">
-        <v>7010502</v>
+        <v>7010469</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9138,6 +9133,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131882928</v>
+        <v>131883769</v>
       </c>
       <c r="B22" t="n">
-        <v>97963</v>
+        <v>57136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,37 +2907,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437191</v>
+        <v>437337</v>
       </c>
       <c r="R22" t="n">
-        <v>7010182</v>
+        <v>7010352</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2964,9 +2969,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131883769</v>
+        <v>131882928</v>
       </c>
       <c r="B23" t="n">
-        <v>57136</v>
+        <v>97963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,42 +3019,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437337</v>
+        <v>437191</v>
       </c>
       <c r="R23" t="n">
-        <v>7010352</v>
+        <v>7010182</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3066,19 +3076,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131883761</v>
+        <v>131883789</v>
       </c>
       <c r="B24" t="n">
-        <v>91892</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,21 +3116,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437164</v>
+        <v>436780</v>
       </c>
       <c r="R24" t="n">
-        <v>7010163</v>
+        <v>7010490</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,10 +3212,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131883789</v>
+        <v>131883761</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,21 +3223,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436780</v>
+        <v>437164</v>
       </c>
       <c r="R25" t="n">
-        <v>7010490</v>
+        <v>7010163</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3426,10 +3426,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131883776</v>
+        <v>131883765</v>
       </c>
       <c r="B27" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3437,34 +3437,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437286</v>
+        <v>437208</v>
       </c>
       <c r="R27" t="n">
-        <v>7010179</v>
+        <v>7010169</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3496,7 +3501,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3506,7 +3511,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,7 +3538,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131882931</v>
+        <v>131883776</v>
       </c>
       <c r="B28" t="n">
         <v>79317</v>
@@ -3564,17 +3569,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436952</v>
+        <v>437286</v>
       </c>
       <c r="R28" t="n">
-        <v>7010316</v>
+        <v>7010179</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3601,9 +3606,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3630,7 +3645,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131883784</v>
+        <v>131882931</v>
       </c>
       <c r="B29" t="n">
         <v>79317</v>
@@ -3661,17 +3676,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436930</v>
+        <v>436952</v>
       </c>
       <c r="R29" t="n">
-        <v>7010353</v>
+        <v>7010316</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3698,19 +3713,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3737,10 +3742,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131883765</v>
+        <v>131883784</v>
       </c>
       <c r="B30" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3748,39 +3753,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437208</v>
+        <v>436930</v>
       </c>
       <c r="R30" t="n">
-        <v>7010169</v>
+        <v>7010353</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4578,48 +4578,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131882926</v>
+        <v>131883768</v>
       </c>
       <c r="B38" t="n">
-        <v>92352</v>
+        <v>57948</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437234</v>
+        <v>437044</v>
       </c>
       <c r="R38" t="n">
-        <v>7010154</v>
+        <v>7010321</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4646,9 +4651,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4675,10 +4690,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131883756</v>
+        <v>131882919</v>
       </c>
       <c r="B39" t="n">
-        <v>78340</v>
+        <v>83297</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4686,37 +4701,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436785</v>
+        <v>436779</v>
       </c>
       <c r="R39" t="n">
-        <v>7010497</v>
+        <v>7010478</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4743,19 +4758,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4782,10 +4787,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131882919</v>
+        <v>131883779</v>
       </c>
       <c r="B40" t="n">
-        <v>83297</v>
+        <v>79317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4793,37 +4798,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436779</v>
+        <v>437081</v>
       </c>
       <c r="R40" t="n">
-        <v>7010478</v>
+        <v>7010232</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4850,9 +4855,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4879,48 +4894,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131883779</v>
+        <v>131882926</v>
       </c>
       <c r="B41" t="n">
-        <v>79317</v>
+        <v>92352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437081</v>
+        <v>437234</v>
       </c>
       <c r="R41" t="n">
-        <v>7010232</v>
+        <v>7010154</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4947,19 +4962,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,10 +4991,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131883768</v>
+        <v>131883756</v>
       </c>
       <c r="B42" t="n">
-        <v>57948</v>
+        <v>78340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,39 +5002,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437044</v>
+        <v>436785</v>
       </c>
       <c r="R42" t="n">
-        <v>7010321</v>
+        <v>7010497</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5195,10 +5195,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131883774</v>
+        <v>131882920</v>
       </c>
       <c r="B44" t="n">
-        <v>91888</v>
+        <v>79936</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,37 +5206,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437103</v>
+        <v>437363</v>
       </c>
       <c r="R44" t="n">
-        <v>7010196</v>
+        <v>7010325</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5263,19 +5263,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131882923</v>
+        <v>131883774</v>
       </c>
       <c r="B45" t="n">
-        <v>91892</v>
+        <v>91888</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5313,37 +5303,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437082</v>
+        <v>437103</v>
       </c>
       <c r="R45" t="n">
-        <v>7010188</v>
+        <v>7010196</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5370,9 +5360,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5399,10 +5399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131882920</v>
+        <v>131882923</v>
       </c>
       <c r="B46" t="n">
-        <v>79936</v>
+        <v>91892</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5410,21 +5410,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437363</v>
+        <v>437082</v>
       </c>
       <c r="R46" t="n">
-        <v>7010325</v>
+        <v>7010188</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131883773</v>
+        <v>131882930</v>
       </c>
       <c r="B47" t="n">
-        <v>92191</v>
+        <v>79317</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436865</v>
+        <v>437227</v>
       </c>
       <c r="R47" t="n">
-        <v>7010395</v>
+        <v>7010158</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5564,19 +5564,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5603,10 +5593,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131883762</v>
+        <v>131883773</v>
       </c>
       <c r="B48" t="n">
-        <v>91892</v>
+        <v>92191</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5614,21 +5604,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5638,10 +5628,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436892</v>
+        <v>436865</v>
       </c>
       <c r="R48" t="n">
-        <v>7010367</v>
+        <v>7010395</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5673,7 +5663,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5683,7 +5673,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5710,10 +5700,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131882930</v>
+        <v>131883762</v>
       </c>
       <c r="B49" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5721,37 +5711,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437227</v>
+        <v>436892</v>
       </c>
       <c r="R49" t="n">
-        <v>7010158</v>
+        <v>7010367</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5778,9 +5768,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5807,10 +5807,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131882925</v>
+        <v>131883764</v>
       </c>
       <c r="B50" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5818,45 +5818,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437206</v>
+        <v>436864</v>
       </c>
       <c r="R50" t="n">
-        <v>7010436</v>
+        <v>7010391</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5883,9 +5875,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6009,10 +6011,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131883764</v>
+        <v>131882925</v>
       </c>
       <c r="B52" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6020,37 +6022,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436864</v>
+        <v>437206</v>
       </c>
       <c r="R52" t="n">
-        <v>7010391</v>
+        <v>7010436</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6077,19 +6087,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7424,32 +7424,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341017</v>
+        <v>132340934</v>
       </c>
       <c r="B66" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436985</v>
+        <v>437567</v>
       </c>
       <c r="R66" t="n">
-        <v>7010332</v>
+        <v>7010358</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,11 +7495,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7526,7 +7521,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341012</v>
+        <v>132341017</v>
       </c>
       <c r="B67" t="n">
         <v>57948</v>
@@ -7561,10 +7556,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436992</v>
+        <v>436985</v>
       </c>
       <c r="R67" t="n">
-        <v>7010454</v>
+        <v>7010332</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7601,7 +7596,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7628,32 +7623,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340934</v>
+        <v>132341012</v>
       </c>
       <c r="B68" t="n">
-        <v>91855</v>
+        <v>57948</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7663,10 +7658,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437567</v>
+        <v>436992</v>
       </c>
       <c r="R68" t="n">
-        <v>7010358</v>
+        <v>7010454</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,6 +7694,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7725,7 +7725,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341008</v>
+        <v>132341009</v>
       </c>
       <c r="B69" t="n">
         <v>57948</v>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437222</v>
+        <v>437127</v>
       </c>
       <c r="R69" t="n">
-        <v>7010260</v>
+        <v>7010372</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7827,7 +7827,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132341009</v>
+        <v>132341008</v>
       </c>
       <c r="B70" t="n">
         <v>57948</v>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437127</v>
+        <v>437222</v>
       </c>
       <c r="R70" t="n">
-        <v>7010372</v>
+        <v>7010260</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131883769</v>
+        <v>131882928</v>
       </c>
       <c r="B22" t="n">
-        <v>57136</v>
+        <v>97963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,42 +2907,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437337</v>
+        <v>437191</v>
       </c>
       <c r="R22" t="n">
-        <v>7010352</v>
+        <v>7010182</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,19 +2964,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131882928</v>
+        <v>131883769</v>
       </c>
       <c r="B23" t="n">
-        <v>97963</v>
+        <v>57136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,37 +3004,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437191</v>
+        <v>437337</v>
       </c>
       <c r="R23" t="n">
-        <v>7010182</v>
+        <v>7010352</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3076,9 +3066,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4578,53 +4578,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131883768</v>
+        <v>131882926</v>
       </c>
       <c r="B38" t="n">
-        <v>57948</v>
+        <v>92352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437044</v>
+        <v>437234</v>
       </c>
       <c r="R38" t="n">
-        <v>7010321</v>
+        <v>7010154</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4651,19 +4646,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4690,10 +4675,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131882919</v>
+        <v>131883756</v>
       </c>
       <c r="B39" t="n">
-        <v>83297</v>
+        <v>78340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4701,37 +4686,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436779</v>
+        <v>436785</v>
       </c>
       <c r="R39" t="n">
-        <v>7010478</v>
+        <v>7010497</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4758,9 +4743,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4787,10 +4782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131883779</v>
+        <v>131883768</v>
       </c>
       <c r="B40" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4798,34 +4793,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437081</v>
+        <v>437044</v>
       </c>
       <c r="R40" t="n">
-        <v>7010232</v>
+        <v>7010321</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4894,32 +4894,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131882926</v>
+        <v>131882919</v>
       </c>
       <c r="B41" t="n">
-        <v>92352</v>
+        <v>83297</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437234</v>
+        <v>436779</v>
       </c>
       <c r="R41" t="n">
-        <v>7010154</v>
+        <v>7010478</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131883756</v>
+        <v>131883779</v>
       </c>
       <c r="B42" t="n">
-        <v>78340</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5002,21 +5002,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436785</v>
+        <v>437081</v>
       </c>
       <c r="R42" t="n">
-        <v>7010497</v>
+        <v>7010232</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341000</v>
+        <v>132341123</v>
       </c>
       <c r="B74" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437046</v>
+        <v>436761</v>
       </c>
       <c r="R74" t="n">
-        <v>7010396</v>
+        <v>7010448</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,11 +8332,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8363,10 +8358,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341002</v>
+        <v>132341124</v>
       </c>
       <c r="B75" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,21 +8369,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437060</v>
+        <v>436893</v>
       </c>
       <c r="R75" t="n">
-        <v>7010387</v>
+        <v>7010302</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8434,11 +8429,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8465,10 +8455,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341123</v>
+        <v>132341000</v>
       </c>
       <c r="B76" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8476,21 +8466,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8500,10 +8490,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436761</v>
+        <v>437046</v>
       </c>
       <c r="R76" t="n">
-        <v>7010448</v>
+        <v>7010396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8536,6 +8526,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8562,10 +8557,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341124</v>
+        <v>132341002</v>
       </c>
       <c r="B77" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8573,21 +8568,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8597,10 +8592,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436893</v>
+        <v>437060</v>
       </c>
       <c r="R77" t="n">
-        <v>7010302</v>
+        <v>7010387</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8633,6 +8628,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9470,10 +9470,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341016</v>
+        <v>132341098</v>
       </c>
       <c r="B86" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436980</v>
+        <v>437162</v>
       </c>
       <c r="R86" t="n">
-        <v>7010332</v>
+        <v>7010098</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9541,11 +9541,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9572,7 +9567,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341010</v>
+        <v>132341016</v>
       </c>
       <c r="B87" t="n">
         <v>57948</v>
@@ -9607,10 +9602,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437123</v>
+        <v>436980</v>
       </c>
       <c r="R87" t="n">
-        <v>7010418</v>
+        <v>7010332</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9647,7 +9642,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9674,7 +9669,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341019</v>
+        <v>132341010</v>
       </c>
       <c r="B88" t="n">
         <v>57948</v>
@@ -9709,10 +9704,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437276</v>
+        <v>437123</v>
       </c>
       <c r="R88" t="n">
-        <v>7010164</v>
+        <v>7010418</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9749,7 +9744,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9776,10 +9771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341098</v>
+        <v>132341019</v>
       </c>
       <c r="B89" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9787,21 +9782,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9811,10 +9806,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437162</v>
+        <v>437276</v>
       </c>
       <c r="R89" t="n">
-        <v>7010098</v>
+        <v>7010164</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9847,6 +9842,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131882928</v>
+        <v>131883769</v>
       </c>
       <c r="B22" t="n">
-        <v>97963</v>
+        <v>57136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,37 +2907,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437191</v>
+        <v>437337</v>
       </c>
       <c r="R22" t="n">
-        <v>7010182</v>
+        <v>7010352</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2964,9 +2969,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131883769</v>
+        <v>131882928</v>
       </c>
       <c r="B23" t="n">
-        <v>57136</v>
+        <v>97963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,42 +3019,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437337</v>
+        <v>437191</v>
       </c>
       <c r="R23" t="n">
-        <v>7010352</v>
+        <v>7010182</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3066,19 +3076,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -9470,10 +9470,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341098</v>
+        <v>132341016</v>
       </c>
       <c r="B86" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437162</v>
+        <v>436980</v>
       </c>
       <c r="R86" t="n">
-        <v>7010098</v>
+        <v>7010332</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9541,6 +9541,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9567,7 +9572,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341016</v>
+        <v>132341010</v>
       </c>
       <c r="B87" t="n">
         <v>57948</v>
@@ -9602,10 +9607,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436980</v>
+        <v>437123</v>
       </c>
       <c r="R87" t="n">
-        <v>7010332</v>
+        <v>7010418</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9642,7 +9647,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9669,7 +9674,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341010</v>
+        <v>132341019</v>
       </c>
       <c r="B88" t="n">
         <v>57948</v>
@@ -9704,10 +9709,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437123</v>
+        <v>437276</v>
       </c>
       <c r="R88" t="n">
-        <v>7010418</v>
+        <v>7010164</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9744,7 +9749,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9771,10 +9776,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341019</v>
+        <v>132341098</v>
       </c>
       <c r="B89" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,21 +9787,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9806,10 +9811,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437276</v>
+        <v>437162</v>
       </c>
       <c r="R89" t="n">
-        <v>7010164</v>
+        <v>7010098</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9842,11 +9847,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -4364,10 +4364,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131883758</v>
+        <v>131883785</v>
       </c>
       <c r="B36" t="n">
-        <v>78340</v>
+        <v>79317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436781</v>
+        <v>436881</v>
       </c>
       <c r="R36" t="n">
-        <v>7010439</v>
+        <v>7010368</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4471,10 +4471,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131883785</v>
+        <v>131883758</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>78340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,21 +4482,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436881</v>
+        <v>436781</v>
       </c>
       <c r="R37" t="n">
-        <v>7010368</v>
+        <v>7010439</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4578,48 +4578,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131882926</v>
+        <v>131883768</v>
       </c>
       <c r="B38" t="n">
-        <v>92352</v>
+        <v>57948</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437234</v>
+        <v>437044</v>
       </c>
       <c r="R38" t="n">
-        <v>7010154</v>
+        <v>7010321</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4646,9 +4651,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4675,10 +4690,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131883756</v>
+        <v>131882919</v>
       </c>
       <c r="B39" t="n">
-        <v>78340</v>
+        <v>83297</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4686,37 +4701,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436785</v>
+        <v>436779</v>
       </c>
       <c r="R39" t="n">
-        <v>7010497</v>
+        <v>7010478</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4743,19 +4758,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4782,10 +4787,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131883768</v>
+        <v>131883779</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4793,39 +4798,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437044</v>
+        <v>437081</v>
       </c>
       <c r="R40" t="n">
-        <v>7010321</v>
+        <v>7010232</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4894,32 +4894,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131882919</v>
+        <v>131882926</v>
       </c>
       <c r="B41" t="n">
-        <v>83297</v>
+        <v>92352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436779</v>
+        <v>437234</v>
       </c>
       <c r="R41" t="n">
-        <v>7010478</v>
+        <v>7010154</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131883779</v>
+        <v>131883756</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>78340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5002,21 +5002,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437081</v>
+        <v>436785</v>
       </c>
       <c r="R42" t="n">
-        <v>7010232</v>
+        <v>7010497</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341123</v>
+        <v>132341000</v>
       </c>
       <c r="B74" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436761</v>
+        <v>437046</v>
       </c>
       <c r="R74" t="n">
-        <v>7010448</v>
+        <v>7010396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,6 +8332,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8358,10 +8363,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341124</v>
+        <v>132341002</v>
       </c>
       <c r="B75" t="n">
-        <v>91888</v>
+        <v>57948</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8369,21 +8374,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8393,10 +8398,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436893</v>
+        <v>437060</v>
       </c>
       <c r="R75" t="n">
-        <v>7010302</v>
+        <v>7010387</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,6 +8434,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8455,10 +8465,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341000</v>
+        <v>132341123</v>
       </c>
       <c r="B76" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8466,21 +8476,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8490,10 +8500,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437046</v>
+        <v>436761</v>
       </c>
       <c r="R76" t="n">
-        <v>7010396</v>
+        <v>7010448</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8526,11 +8536,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8557,10 +8562,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341002</v>
+        <v>132341124</v>
       </c>
       <c r="B77" t="n">
-        <v>57948</v>
+        <v>91888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8568,21 +8573,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8592,10 +8597,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437060</v>
+        <v>436893</v>
       </c>
       <c r="R77" t="n">
-        <v>7010387</v>
+        <v>7010302</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8628,11 +8633,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>131883760</v>
       </c>
       <c r="B11" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>131883788</v>
       </c>
       <c r="B12" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131883780</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>131882924</v>
       </c>
       <c r="B14" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>131883767</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131883755</v>
       </c>
       <c r="B16" t="n">
-        <v>78340</v>
+        <v>78342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>131883777</v>
       </c>
       <c r="B17" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>131883782</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>131883759</v>
       </c>
       <c r="B19" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>131883766</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>131883786</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131883769</v>
+        <v>131882928</v>
       </c>
       <c r="B22" t="n">
-        <v>57136</v>
+        <v>97971</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,42 +2907,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437337</v>
+        <v>437191</v>
       </c>
       <c r="R22" t="n">
-        <v>7010352</v>
+        <v>7010182</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,19 +2964,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131882928</v>
+        <v>131883769</v>
       </c>
       <c r="B23" t="n">
-        <v>97963</v>
+        <v>57137</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,37 +3004,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437191</v>
+        <v>437337</v>
       </c>
       <c r="R23" t="n">
-        <v>7010182</v>
+        <v>7010352</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3076,9 +3066,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131883789</v>
+        <v>131883761</v>
       </c>
       <c r="B24" t="n">
-        <v>79317</v>
+        <v>91898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,21 +3116,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436780</v>
+        <v>437164</v>
       </c>
       <c r="R24" t="n">
-        <v>7010490</v>
+        <v>7010163</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,10 +3212,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131883761</v>
+        <v>131883789</v>
       </c>
       <c r="B25" t="n">
-        <v>91892</v>
+        <v>79319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,21 +3223,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437164</v>
+        <v>436780</v>
       </c>
       <c r="R25" t="n">
-        <v>7010163</v>
+        <v>7010490</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,7 +3322,7 @@
         <v>131883775</v>
       </c>
       <c r="B26" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131883765</v>
+        <v>131883776</v>
       </c>
       <c r="B27" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3437,39 +3437,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437208</v>
+        <v>437286</v>
       </c>
       <c r="R27" t="n">
-        <v>7010169</v>
+        <v>7010179</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3501,7 +3496,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3511,7 +3506,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3538,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131883776</v>
+        <v>131882931</v>
       </c>
       <c r="B28" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,17 +3564,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437286</v>
+        <v>436952</v>
       </c>
       <c r="R28" t="n">
-        <v>7010179</v>
+        <v>7010316</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3606,19 +3601,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,10 +3630,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131882931</v>
+        <v>131883784</v>
       </c>
       <c r="B29" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3676,17 +3661,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436952</v>
+        <v>436930</v>
       </c>
       <c r="R29" t="n">
-        <v>7010316</v>
+        <v>7010353</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3713,9 +3698,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3742,10 +3737,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131883784</v>
+        <v>131883765</v>
       </c>
       <c r="B30" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,34 +3748,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436930</v>
+        <v>437208</v>
       </c>
       <c r="R30" t="n">
-        <v>7010353</v>
+        <v>7010169</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3849,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131883787</v>
+        <v>131882927</v>
       </c>
       <c r="B31" t="n">
-        <v>79317</v>
+        <v>92197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,37 +3860,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436824</v>
+        <v>437098</v>
       </c>
       <c r="R31" t="n">
-        <v>7010448</v>
+        <v>7010473</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3917,19 +3917,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3956,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131883778</v>
+        <v>131882917</v>
       </c>
       <c r="B32" t="n">
-        <v>79317</v>
+        <v>78342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,37 +3957,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437111</v>
+        <v>437024</v>
       </c>
       <c r="R32" t="n">
-        <v>7010195</v>
+        <v>7010309</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4024,19 +4014,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4063,10 +4043,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131882927</v>
+        <v>131883787</v>
       </c>
       <c r="B33" t="n">
-        <v>92191</v>
+        <v>79319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,37 +4054,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437098</v>
+        <v>436824</v>
       </c>
       <c r="R33" t="n">
-        <v>7010473</v>
+        <v>7010448</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4131,9 +4111,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,10 +4150,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131882917</v>
+        <v>131883778</v>
       </c>
       <c r="B34" t="n">
-        <v>78340</v>
+        <v>79319</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4171,37 +4161,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437024</v>
+        <v>437111</v>
       </c>
       <c r="R34" t="n">
-        <v>7010309</v>
+        <v>7010195</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,9 +4218,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,7 +4260,7 @@
         <v>131883781</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131883785</v>
+        <v>131883758</v>
       </c>
       <c r="B36" t="n">
-        <v>79317</v>
+        <v>78342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436881</v>
+        <v>436781</v>
       </c>
       <c r="R36" t="n">
-        <v>7010368</v>
+        <v>7010439</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4471,10 +4471,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131883758</v>
+        <v>131883785</v>
       </c>
       <c r="B37" t="n">
-        <v>78340</v>
+        <v>79319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4482,21 +4482,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436781</v>
+        <v>436881</v>
       </c>
       <c r="R37" t="n">
-        <v>7010439</v>
+        <v>7010368</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131883768</v>
+        <v>131882919</v>
       </c>
       <c r="B38" t="n">
-        <v>57948</v>
+        <v>83299</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4589,42 +4589,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437044</v>
+        <v>436779</v>
       </c>
       <c r="R38" t="n">
-        <v>7010321</v>
+        <v>7010478</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4651,19 +4646,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4690,10 +4675,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131882919</v>
+        <v>131883779</v>
       </c>
       <c r="B39" t="n">
-        <v>83297</v>
+        <v>79319</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4701,37 +4686,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436779</v>
+        <v>437081</v>
       </c>
       <c r="R39" t="n">
-        <v>7010478</v>
+        <v>7010232</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4758,9 +4743,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4787,48 +4782,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131883779</v>
+        <v>131882926</v>
       </c>
       <c r="B40" t="n">
-        <v>79317</v>
+        <v>92358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437081</v>
+        <v>437234</v>
       </c>
       <c r="R40" t="n">
-        <v>7010232</v>
+        <v>7010154</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,19 +4850,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4894,48 +4879,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131882926</v>
+        <v>131883756</v>
       </c>
       <c r="B41" t="n">
-        <v>92352</v>
+        <v>78342</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437234</v>
+        <v>436785</v>
       </c>
       <c r="R41" t="n">
-        <v>7010154</v>
+        <v>7010497</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4962,9 +4947,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4991,10 +4986,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131883756</v>
+        <v>131883768</v>
       </c>
       <c r="B42" t="n">
-        <v>78340</v>
+        <v>57949</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5002,34 +4997,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436785</v>
+        <v>437044</v>
       </c>
       <c r="R42" t="n">
-        <v>7010497</v>
+        <v>7010321</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5101,7 +5101,7 @@
         <v>131882932</v>
       </c>
       <c r="B43" t="n">
-        <v>83289</v>
+        <v>83291</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>131882920</v>
       </c>
       <c r="B44" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>131883774</v>
       </c>
       <c r="B45" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>131882923</v>
       </c>
       <c r="B46" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>131882930</v>
       </c>
       <c r="B47" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>131883773</v>
       </c>
       <c r="B48" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>131883762</v>
       </c>
       <c r="B49" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>131883764</v>
       </c>
       <c r="B50" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5914,10 +5914,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131882921</v>
+        <v>131882925</v>
       </c>
       <c r="B51" t="n">
-        <v>79907</v>
+        <v>57949</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5925,34 +5925,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437362</v>
+        <v>437206</v>
       </c>
       <c r="R51" t="n">
-        <v>7010336</v>
+        <v>7010436</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6011,10 +6019,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131882925</v>
+        <v>131882921</v>
       </c>
       <c r="B52" t="n">
-        <v>57948</v>
+        <v>79909</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,42 +6030,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437206</v>
+        <v>437362</v>
       </c>
       <c r="R52" t="n">
-        <v>7010436</v>
+        <v>7010336</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6119,7 +6119,7 @@
         <v>131882929</v>
       </c>
       <c r="B53" t="n">
-        <v>92264</v>
+        <v>92270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>131882922</v>
       </c>
       <c r="B54" t="n">
-        <v>92264</v>
+        <v>92270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>132341092</v>
       </c>
       <c r="B55" t="n">
-        <v>92620</v>
+        <v>92626</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6409,10 +6409,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341014</v>
+        <v>132341003</v>
       </c>
       <c r="B56" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6444,10 +6444,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436800</v>
+        <v>437074</v>
       </c>
       <c r="R56" t="n">
-        <v>7010351</v>
+        <v>7010349</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6511,10 +6511,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341003</v>
+        <v>132341014</v>
       </c>
       <c r="B57" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437074</v>
+        <v>436800</v>
       </c>
       <c r="R57" t="n">
-        <v>7010349</v>
+        <v>7010351</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6616,7 +6616,7 @@
         <v>132341099</v>
       </c>
       <c r="B58" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>132341007</v>
       </c>
       <c r="B59" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341022</v>
+        <v>132341024</v>
       </c>
       <c r="B60" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437263</v>
+        <v>437284</v>
       </c>
       <c r="R60" t="n">
-        <v>7010455</v>
+        <v>7010437</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6917,7 +6917,7 @@
         <v>132341006</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7016,10 +7016,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341024</v>
+        <v>132341022</v>
       </c>
       <c r="B62" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437284</v>
+        <v>437263</v>
       </c>
       <c r="R62" t="n">
-        <v>7010437</v>
+        <v>7010455</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7121,7 +7121,7 @@
         <v>132341025</v>
       </c>
       <c r="B63" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>132341013</v>
       </c>
       <c r="B64" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>132341026</v>
       </c>
       <c r="B65" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7424,32 +7424,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132340934</v>
+        <v>132341012</v>
       </c>
       <c r="B66" t="n">
-        <v>91855</v>
+        <v>57949</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437567</v>
+        <v>436992</v>
       </c>
       <c r="R66" t="n">
-        <v>7010358</v>
+        <v>7010454</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,6 +7495,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7524,7 +7529,7 @@
         <v>132341017</v>
       </c>
       <c r="B67" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7623,32 +7628,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341012</v>
+        <v>132340934</v>
       </c>
       <c r="B68" t="n">
-        <v>57948</v>
+        <v>91861</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7658,10 +7663,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436992</v>
+        <v>437567</v>
       </c>
       <c r="R68" t="n">
-        <v>7010454</v>
+        <v>7010358</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7694,11 +7699,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7728,7 +7728,7 @@
         <v>132341009</v>
       </c>
       <c r="B69" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>132341008</v>
       </c>
       <c r="B70" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>132340950</v>
       </c>
       <c r="B71" t="n">
-        <v>92615</v>
+        <v>92621</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132341093</v>
+        <v>132340999</v>
       </c>
       <c r="B72" t="n">
-        <v>57945</v>
+        <v>57949</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8060,10 +8060,14 @@
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8077,10 +8081,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437170</v>
+        <v>436960</v>
       </c>
       <c r="R72" t="n">
-        <v>7010069</v>
+        <v>7010414</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8113,6 +8117,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8139,10 +8148,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132340999</v>
+        <v>132341093</v>
       </c>
       <c r="B73" t="n">
-        <v>57948</v>
+        <v>57946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8150,16 +8159,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8173,14 +8182,10 @@
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8194,10 +8199,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436960</v>
+        <v>437170</v>
       </c>
       <c r="R73" t="n">
-        <v>7010414</v>
+        <v>7010069</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8230,11 +8235,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341000</v>
+        <v>132341002</v>
       </c>
       <c r="B74" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437046</v>
+        <v>437060</v>
       </c>
       <c r="R74" t="n">
-        <v>7010396</v>
+        <v>7010387</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8363,10 +8363,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341002</v>
+        <v>132341000</v>
       </c>
       <c r="B75" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437060</v>
+        <v>437046</v>
       </c>
       <c r="R75" t="n">
-        <v>7010387</v>
+        <v>7010396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8468,7 +8468,7 @@
         <v>132341123</v>
       </c>
       <c r="B76" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>132341124</v>
       </c>
       <c r="B77" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>132341021</v>
       </c>
       <c r="B78" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>132341015</v>
       </c>
       <c r="B79" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>132341122</v>
       </c>
       <c r="B80" t="n">
-        <v>91888</v>
+        <v>91894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>132341001</v>
       </c>
       <c r="B81" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>132341011</v>
       </c>
       <c r="B82" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9164,10 +9164,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341023</v>
+        <v>132341020</v>
       </c>
       <c r="B83" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437277</v>
+        <v>437311</v>
       </c>
       <c r="R83" t="n">
-        <v>7010440</v>
+        <v>7010307</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9266,10 +9266,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341020</v>
+        <v>132341004</v>
       </c>
       <c r="B84" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437311</v>
+        <v>437121</v>
       </c>
       <c r="R84" t="n">
-        <v>7010307</v>
+        <v>7010310</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9368,10 +9368,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341004</v>
+        <v>132341023</v>
       </c>
       <c r="B85" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437121</v>
+        <v>437277</v>
       </c>
       <c r="R85" t="n">
-        <v>7010310</v>
+        <v>7010440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9470,10 +9470,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341016</v>
+        <v>132341098</v>
       </c>
       <c r="B86" t="n">
-        <v>57948</v>
+        <v>92197</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436980</v>
+        <v>437162</v>
       </c>
       <c r="R86" t="n">
-        <v>7010332</v>
+        <v>7010098</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9541,11 +9541,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9572,10 +9567,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341010</v>
+        <v>132341016</v>
       </c>
       <c r="B87" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9607,10 +9602,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437123</v>
+        <v>436980</v>
       </c>
       <c r="R87" t="n">
-        <v>7010418</v>
+        <v>7010332</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9647,7 +9642,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9674,10 +9669,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341019</v>
+        <v>132341010</v>
       </c>
       <c r="B88" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9709,10 +9704,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437276</v>
+        <v>437123</v>
       </c>
       <c r="R88" t="n">
-        <v>7010164</v>
+        <v>7010418</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9749,7 +9744,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9776,10 +9771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341098</v>
+        <v>132341019</v>
       </c>
       <c r="B89" t="n">
-        <v>92191</v>
+        <v>57949</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9787,21 +9782,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9811,10 +9806,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437162</v>
+        <v>437276</v>
       </c>
       <c r="R89" t="n">
-        <v>7010098</v>
+        <v>7010164</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9847,6 +9842,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9876,7 +9876,7 @@
         <v>132341018</v>
       </c>
       <c r="B90" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341002</v>
+        <v>132341123</v>
       </c>
       <c r="B74" t="n">
-        <v>57949</v>
+        <v>91894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437060</v>
+        <v>436761</v>
       </c>
       <c r="R74" t="n">
-        <v>7010387</v>
+        <v>7010448</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,11 +8332,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8363,10 +8358,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341000</v>
+        <v>132341124</v>
       </c>
       <c r="B75" t="n">
-        <v>57949</v>
+        <v>91894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,21 +8369,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437046</v>
+        <v>436893</v>
       </c>
       <c r="R75" t="n">
-        <v>7010396</v>
+        <v>7010302</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8434,11 +8429,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8465,10 +8455,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341123</v>
+        <v>132341002</v>
       </c>
       <c r="B76" t="n">
-        <v>91894</v>
+        <v>57949</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8476,21 +8466,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8500,10 +8490,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436761</v>
+        <v>437060</v>
       </c>
       <c r="R76" t="n">
-        <v>7010448</v>
+        <v>7010387</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8536,6 +8526,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8562,10 +8557,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341124</v>
+        <v>132341000</v>
       </c>
       <c r="B77" t="n">
-        <v>91894</v>
+        <v>57949</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8573,21 +8568,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8597,10 +8592,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436893</v>
+        <v>437046</v>
       </c>
       <c r="R77" t="n">
-        <v>7010302</v>
+        <v>7010396</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8633,6 +8628,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -6119,7 +6119,7 @@
         <v>131882929</v>
       </c>
       <c r="B53" t="n">
-        <v>92270</v>
+        <v>92280</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>131882922</v>
       </c>
       <c r="B54" t="n">
-        <v>92270</v>
+        <v>92280</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>132341092</v>
       </c>
       <c r="B55" t="n">
-        <v>92626</v>
+        <v>92636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>132341003</v>
       </c>
       <c r="B56" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>132341014</v>
       </c>
       <c r="B57" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341099</v>
+        <v>132341007</v>
       </c>
       <c r="B58" t="n">
-        <v>92197</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6624,21 +6624,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437567</v>
+        <v>437143</v>
       </c>
       <c r="R58" t="n">
-        <v>7010357</v>
+        <v>7010271</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6684,6 +6684,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6710,10 +6715,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341007</v>
+        <v>132341099</v>
       </c>
       <c r="B59" t="n">
-        <v>57949</v>
+        <v>92207</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6721,21 +6726,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6745,10 +6750,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437143</v>
+        <v>437567</v>
       </c>
       <c r="R59" t="n">
-        <v>7010271</v>
+        <v>7010357</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6781,11 +6786,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6812,10 +6812,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341024</v>
+        <v>132341022</v>
       </c>
       <c r="B60" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437284</v>
+        <v>437263</v>
       </c>
       <c r="R60" t="n">
-        <v>7010437</v>
+        <v>7010455</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6917,7 +6917,7 @@
         <v>132341006</v>
       </c>
       <c r="B61" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7016,10 +7016,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341022</v>
+        <v>132341024</v>
       </c>
       <c r="B62" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437263</v>
+        <v>437284</v>
       </c>
       <c r="R62" t="n">
-        <v>7010455</v>
+        <v>7010437</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7121,7 +7121,7 @@
         <v>132341025</v>
       </c>
       <c r="B63" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>132341013</v>
       </c>
       <c r="B64" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>132341026</v>
       </c>
       <c r="B65" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7424,10 +7424,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341012</v>
+        <v>132341017</v>
       </c>
       <c r="B66" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436992</v>
+        <v>436985</v>
       </c>
       <c r="R66" t="n">
-        <v>7010454</v>
+        <v>7010332</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7526,10 +7526,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341017</v>
+        <v>132341012</v>
       </c>
       <c r="B67" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436985</v>
+        <v>436992</v>
       </c>
       <c r="R67" t="n">
-        <v>7010332</v>
+        <v>7010454</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7631,7 +7631,7 @@
         <v>132340934</v>
       </c>
       <c r="B68" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>132341009</v>
       </c>
       <c r="B69" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>132341008</v>
       </c>
       <c r="B70" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>132340950</v>
       </c>
       <c r="B71" t="n">
-        <v>92621</v>
+        <v>92631</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340999</v>
+        <v>132341093</v>
       </c>
       <c r="B72" t="n">
-        <v>57949</v>
+        <v>57950</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8060,14 +8060,10 @@
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8081,10 +8077,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436960</v>
+        <v>437170</v>
       </c>
       <c r="R72" t="n">
-        <v>7010414</v>
+        <v>7010069</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8117,11 +8113,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8148,10 +8139,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341093</v>
+        <v>132340999</v>
       </c>
       <c r="B73" t="n">
-        <v>57946</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8159,16 +8150,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8182,10 +8173,14 @@
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8199,10 +8194,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437170</v>
+        <v>436960</v>
       </c>
       <c r="R73" t="n">
-        <v>7010069</v>
+        <v>7010414</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8235,6 +8230,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8264,7 +8264,7 @@
         <v>132341123</v>
       </c>
       <c r="B74" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>132341124</v>
       </c>
       <c r="B75" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8455,10 +8455,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341002</v>
+        <v>132341000</v>
       </c>
       <c r="B76" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437060</v>
+        <v>437046</v>
       </c>
       <c r="R76" t="n">
-        <v>7010387</v>
+        <v>7010396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8557,10 +8557,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341000</v>
+        <v>132341002</v>
       </c>
       <c r="B77" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437046</v>
+        <v>437060</v>
       </c>
       <c r="R77" t="n">
-        <v>7010396</v>
+        <v>7010387</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8662,7 +8662,7 @@
         <v>132341021</v>
       </c>
       <c r="B78" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>132341015</v>
       </c>
       <c r="B79" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>132341122</v>
       </c>
       <c r="B80" t="n">
-        <v>91894</v>
+        <v>91904</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8960,10 +8960,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341001</v>
+        <v>132341011</v>
       </c>
       <c r="B81" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437047</v>
+        <v>437059</v>
       </c>
       <c r="R81" t="n">
-        <v>7010396</v>
+        <v>7010469</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341011</v>
+        <v>132341001</v>
       </c>
       <c r="B82" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437059</v>
+        <v>437047</v>
       </c>
       <c r="R82" t="n">
-        <v>7010469</v>
+        <v>7010396</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9164,10 +9164,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341020</v>
+        <v>132341023</v>
       </c>
       <c r="B83" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437311</v>
+        <v>437277</v>
       </c>
       <c r="R83" t="n">
-        <v>7010307</v>
+        <v>7010440</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9266,10 +9266,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341004</v>
+        <v>132341020</v>
       </c>
       <c r="B84" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437121</v>
+        <v>437311</v>
       </c>
       <c r="R84" t="n">
-        <v>7010310</v>
+        <v>7010307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9368,10 +9368,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341023</v>
+        <v>132341004</v>
       </c>
       <c r="B85" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437277</v>
+        <v>437121</v>
       </c>
       <c r="R85" t="n">
-        <v>7010440</v>
+        <v>7010310</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9470,10 +9470,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341098</v>
+        <v>132341019</v>
       </c>
       <c r="B86" t="n">
-        <v>92197</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437162</v>
+        <v>437276</v>
       </c>
       <c r="R86" t="n">
-        <v>7010098</v>
+        <v>7010164</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9541,6 +9541,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9567,10 +9572,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341016</v>
+        <v>132341098</v>
       </c>
       <c r="B87" t="n">
-        <v>57949</v>
+        <v>92207</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9578,21 +9583,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9602,10 +9607,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436980</v>
+        <v>437162</v>
       </c>
       <c r="R87" t="n">
-        <v>7010332</v>
+        <v>7010098</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9638,11 +9643,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9669,10 +9669,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341010</v>
+        <v>132341016</v>
       </c>
       <c r="B88" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9704,10 +9704,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437123</v>
+        <v>436980</v>
       </c>
       <c r="R88" t="n">
-        <v>7010418</v>
+        <v>7010332</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9771,10 +9771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341019</v>
+        <v>132341010</v>
       </c>
       <c r="B89" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9806,10 +9806,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437276</v>
+        <v>437123</v>
       </c>
       <c r="R89" t="n">
-        <v>7010164</v>
+        <v>7010418</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9876,7 +9876,7 @@
         <v>132341018</v>
       </c>
       <c r="B90" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -6314,7 +6314,7 @@
         <v>132341092</v>
       </c>
       <c r="B55" t="n">
-        <v>92636</v>
+        <v>92637</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341007</v>
+        <v>132341099</v>
       </c>
       <c r="B58" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6624,21 +6624,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437143</v>
+        <v>437567</v>
       </c>
       <c r="R58" t="n">
-        <v>7010271</v>
+        <v>7010357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6684,11 +6684,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6715,10 +6710,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341099</v>
+        <v>132341007</v>
       </c>
       <c r="B59" t="n">
-        <v>92207</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6726,21 +6721,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6750,10 +6745,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437567</v>
+        <v>437143</v>
       </c>
       <c r="R59" t="n">
-        <v>7010357</v>
+        <v>7010271</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6786,6 +6781,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6812,7 +6812,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341022</v>
+        <v>132341024</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437263</v>
+        <v>437284</v>
       </c>
       <c r="R60" t="n">
-        <v>7010455</v>
+        <v>7010437</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7016,7 +7016,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341024</v>
+        <v>132341022</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437284</v>
+        <v>437263</v>
       </c>
       <c r="R62" t="n">
-        <v>7010437</v>
+        <v>7010455</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7424,32 +7424,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341017</v>
+        <v>132340934</v>
       </c>
       <c r="B66" t="n">
-        <v>57953</v>
+        <v>91872</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436985</v>
+        <v>437567</v>
       </c>
       <c r="R66" t="n">
-        <v>7010332</v>
+        <v>7010358</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,11 +7495,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7628,32 +7623,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340934</v>
+        <v>132341017</v>
       </c>
       <c r="B68" t="n">
-        <v>91871</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7663,10 +7658,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437567</v>
+        <v>436985</v>
       </c>
       <c r="R68" t="n">
-        <v>7010358</v>
+        <v>7010332</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,6 +7694,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7932,7 +7932,7 @@
         <v>132340950</v>
       </c>
       <c r="B71" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132341093</v>
+        <v>132340999</v>
       </c>
       <c r="B72" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8060,10 +8060,14 @@
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8077,10 +8081,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437170</v>
+        <v>436960</v>
       </c>
       <c r="R72" t="n">
-        <v>7010069</v>
+        <v>7010414</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8113,6 +8117,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8139,10 +8148,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132340999</v>
+        <v>132341093</v>
       </c>
       <c r="B73" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8150,16 +8159,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8173,14 +8182,10 @@
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8194,10 +8199,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436960</v>
+        <v>437170</v>
       </c>
       <c r="R73" t="n">
-        <v>7010414</v>
+        <v>7010069</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8230,11 +8235,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8264,7 +8264,7 @@
         <v>132341123</v>
       </c>
       <c r="B74" t="n">
-        <v>91904</v>
+        <v>91905</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>132341124</v>
       </c>
       <c r="B75" t="n">
-        <v>91904</v>
+        <v>91905</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341000</v>
+        <v>132341002</v>
       </c>
       <c r="B76" t="n">
         <v>57953</v>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437046</v>
+        <v>437060</v>
       </c>
       <c r="R76" t="n">
-        <v>7010396</v>
+        <v>7010387</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8557,7 +8557,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341002</v>
+        <v>132341000</v>
       </c>
       <c r="B77" t="n">
         <v>57953</v>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437060</v>
+        <v>437046</v>
       </c>
       <c r="R77" t="n">
-        <v>7010387</v>
+        <v>7010396</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8863,10 +8863,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341122</v>
+        <v>132341001</v>
       </c>
       <c r="B80" t="n">
-        <v>91904</v>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8874,21 +8874,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436784</v>
+        <v>437047</v>
       </c>
       <c r="R80" t="n">
-        <v>7010502</v>
+        <v>7010396</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8934,6 +8934,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9062,10 +9067,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341001</v>
+        <v>132341122</v>
       </c>
       <c r="B82" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9073,21 +9078,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9097,10 +9102,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437047</v>
+        <v>436784</v>
       </c>
       <c r="R82" t="n">
-        <v>7010396</v>
+        <v>7010502</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9133,11 +9138,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9164,7 +9164,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341023</v>
+        <v>132341020</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437277</v>
+        <v>437311</v>
       </c>
       <c r="R83" t="n">
-        <v>7010440</v>
+        <v>7010307</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341020</v>
+        <v>132341004</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437311</v>
+        <v>437121</v>
       </c>
       <c r="R84" t="n">
-        <v>7010307</v>
+        <v>7010310</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9368,7 +9368,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341004</v>
+        <v>132341023</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -9403,10 +9403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437121</v>
+        <v>437277</v>
       </c>
       <c r="R85" t="n">
-        <v>7010310</v>
+        <v>7010440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341019</v>
+        <v>132341016</v>
       </c>
       <c r="B86" t="n">
         <v>57953</v>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437276</v>
+        <v>436980</v>
       </c>
       <c r="R86" t="n">
-        <v>7010164</v>
+        <v>7010332</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9572,10 +9572,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341098</v>
+        <v>132341010</v>
       </c>
       <c r="B87" t="n">
-        <v>92207</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9583,21 +9583,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437162</v>
+        <v>437123</v>
       </c>
       <c r="R87" t="n">
-        <v>7010098</v>
+        <v>7010418</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9643,6 +9643,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9669,7 +9674,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341016</v>
+        <v>132341019</v>
       </c>
       <c r="B88" t="n">
         <v>57953</v>
@@ -9704,10 +9709,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436980</v>
+        <v>437276</v>
       </c>
       <c r="R88" t="n">
-        <v>7010332</v>
+        <v>7010164</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9744,7 +9749,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9771,10 +9776,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341010</v>
+        <v>132341098</v>
       </c>
       <c r="B89" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,21 +9787,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9806,10 +9811,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437123</v>
+        <v>437162</v>
       </c>
       <c r="R89" t="n">
-        <v>7010418</v>
+        <v>7010098</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9842,11 +9847,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -6119,7 +6119,7 @@
         <v>131882929</v>
       </c>
       <c r="B53" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>131882922</v>
       </c>
       <c r="B54" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341003</v>
+        <v>132341014</v>
       </c>
       <c r="B56" t="n">
         <v>57953</v>
@@ -6444,10 +6444,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437074</v>
+        <v>436800</v>
       </c>
       <c r="R56" t="n">
-        <v>7010349</v>
+        <v>7010351</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6511,7 +6511,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341014</v>
+        <v>132341003</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436800</v>
+        <v>437074</v>
       </c>
       <c r="R57" t="n">
-        <v>7010351</v>
+        <v>7010349</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6812,7 +6812,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341024</v>
+        <v>132341006</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437284</v>
+        <v>437113</v>
       </c>
       <c r="R60" t="n">
-        <v>7010437</v>
+        <v>7010291</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341006</v>
+        <v>132341024</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437113</v>
+        <v>437284</v>
       </c>
       <c r="R61" t="n">
-        <v>7010291</v>
+        <v>7010437</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7521,7 +7521,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341012</v>
+        <v>132341017</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -7556,10 +7556,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436992</v>
+        <v>436985</v>
       </c>
       <c r="R67" t="n">
-        <v>7010454</v>
+        <v>7010332</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7623,7 +7623,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341017</v>
+        <v>132341012</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -7658,10 +7658,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436985</v>
+        <v>436992</v>
       </c>
       <c r="R68" t="n">
-        <v>7010332</v>
+        <v>7010454</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8026,10 +8026,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132340999</v>
+        <v>132341093</v>
       </c>
       <c r="B72" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8060,14 +8060,10 @@
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8081,10 +8077,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436960</v>
+        <v>437170</v>
       </c>
       <c r="R72" t="n">
-        <v>7010414</v>
+        <v>7010069</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8117,11 +8113,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8148,10 +8139,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132341093</v>
+        <v>132340999</v>
       </c>
       <c r="B73" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8159,16 +8150,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8182,10 +8173,14 @@
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8199,10 +8194,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437170</v>
+        <v>436960</v>
       </c>
       <c r="R73" t="n">
-        <v>7010069</v>
+        <v>7010414</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8235,6 +8230,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341123</v>
+        <v>132341000</v>
       </c>
       <c r="B74" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436761</v>
+        <v>437046</v>
       </c>
       <c r="R74" t="n">
-        <v>7010448</v>
+        <v>7010396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,6 +8332,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8358,10 +8363,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341124</v>
+        <v>132341002</v>
       </c>
       <c r="B75" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8369,21 +8374,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8393,10 +8398,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436893</v>
+        <v>437060</v>
       </c>
       <c r="R75" t="n">
-        <v>7010302</v>
+        <v>7010387</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,6 +8434,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8455,10 +8465,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341002</v>
+        <v>132341123</v>
       </c>
       <c r="B76" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8466,21 +8476,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8490,10 +8500,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437060</v>
+        <v>436761</v>
       </c>
       <c r="R76" t="n">
-        <v>7010387</v>
+        <v>7010448</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8526,11 +8536,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8557,10 +8562,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341000</v>
+        <v>132341124</v>
       </c>
       <c r="B77" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8568,21 +8573,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8592,10 +8597,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437046</v>
+        <v>436893</v>
       </c>
       <c r="R77" t="n">
-        <v>7010396</v>
+        <v>7010302</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8628,11 +8633,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8863,10 +8863,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341001</v>
+        <v>132341122</v>
       </c>
       <c r="B80" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8874,21 +8874,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437047</v>
+        <v>436784</v>
       </c>
       <c r="R80" t="n">
-        <v>7010396</v>
+        <v>7010502</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8934,11 +8934,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8965,7 +8960,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341011</v>
+        <v>132341001</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -9000,10 +8995,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437059</v>
+        <v>437047</v>
       </c>
       <c r="R81" t="n">
-        <v>7010469</v>
+        <v>7010396</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9067,10 +9062,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341122</v>
+        <v>132341011</v>
       </c>
       <c r="B82" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9078,21 +9073,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9102,10 +9097,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436784</v>
+        <v>437059</v>
       </c>
       <c r="R82" t="n">
-        <v>7010502</v>
+        <v>7010469</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9138,6 +9133,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9164,7 +9164,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341020</v>
+        <v>132341023</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437311</v>
+        <v>437277</v>
       </c>
       <c r="R83" t="n">
-        <v>7010307</v>
+        <v>7010440</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341004</v>
+        <v>132341020</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437121</v>
+        <v>437311</v>
       </c>
       <c r="R84" t="n">
-        <v>7010310</v>
+        <v>7010307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9368,7 +9368,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341023</v>
+        <v>132341004</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -9403,10 +9403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437277</v>
+        <v>437121</v>
       </c>
       <c r="R85" t="n">
-        <v>7010440</v>
+        <v>7010310</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341000</v>
+        <v>132341123</v>
       </c>
       <c r="B74" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437046</v>
+        <v>436761</v>
       </c>
       <c r="R74" t="n">
-        <v>7010396</v>
+        <v>7010448</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,11 +8332,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8363,10 +8358,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341002</v>
+        <v>132341124</v>
       </c>
       <c r="B75" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8374,21 +8369,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437060</v>
+        <v>436893</v>
       </c>
       <c r="R75" t="n">
-        <v>7010387</v>
+        <v>7010302</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8434,11 +8429,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8465,10 +8455,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341123</v>
+        <v>132341000</v>
       </c>
       <c r="B76" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8476,21 +8466,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8500,10 +8490,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436761</v>
+        <v>437046</v>
       </c>
       <c r="R76" t="n">
-        <v>7010448</v>
+        <v>7010396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8536,6 +8526,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8562,10 +8557,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341124</v>
+        <v>132341002</v>
       </c>
       <c r="B77" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8573,21 +8568,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8597,10 +8592,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436893</v>
+        <v>437060</v>
       </c>
       <c r="R77" t="n">
-        <v>7010302</v>
+        <v>7010387</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8633,6 +8628,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9973,6 +9973,113 @@
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132796665</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>437176</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7010505</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -6311,32 +6311,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341092</v>
+        <v>132341003</v>
       </c>
       <c r="B55" t="n">
-        <v>92637</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437194</v>
+        <v>437074</v>
       </c>
       <c r="R55" t="n">
-        <v>7010065</v>
+        <v>7010349</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,13 +6384,17 @@
           <t>2026-04-07</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6511,32 +6515,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341003</v>
+        <v>132341092</v>
       </c>
       <c r="B57" t="n">
-        <v>57953</v>
+        <v>92637</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6546,10 +6550,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437074</v>
+        <v>437194</v>
       </c>
       <c r="R57" t="n">
-        <v>7010349</v>
+        <v>7010065</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6584,17 +6588,13 @@
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6812,7 +6812,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341006</v>
+        <v>132341024</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437113</v>
+        <v>437284</v>
       </c>
       <c r="R60" t="n">
-        <v>7010291</v>
+        <v>7010437</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341024</v>
+        <v>132341006</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437284</v>
+        <v>437113</v>
       </c>
       <c r="R61" t="n">
-        <v>7010437</v>
+        <v>7010291</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7424,32 +7424,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132340934</v>
+        <v>132341012</v>
       </c>
       <c r="B66" t="n">
-        <v>91872</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437567</v>
+        <v>436992</v>
       </c>
       <c r="R66" t="n">
-        <v>7010358</v>
+        <v>7010454</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,6 +7495,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7623,32 +7628,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341012</v>
+        <v>132340934</v>
       </c>
       <c r="B68" t="n">
-        <v>57953</v>
+        <v>91872</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7658,10 +7663,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436992</v>
+        <v>437567</v>
       </c>
       <c r="R68" t="n">
-        <v>7010454</v>
+        <v>7010358</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7694,11 +7699,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341123</v>
+        <v>132341002</v>
       </c>
       <c r="B74" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436761</v>
+        <v>437060</v>
       </c>
       <c r="R74" t="n">
-        <v>7010448</v>
+        <v>7010387</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,6 +8332,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8358,10 +8363,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341124</v>
+        <v>132341000</v>
       </c>
       <c r="B75" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8369,21 +8374,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8393,10 +8398,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436893</v>
+        <v>437046</v>
       </c>
       <c r="R75" t="n">
-        <v>7010302</v>
+        <v>7010396</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,6 +8434,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8455,10 +8465,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341000</v>
+        <v>132341123</v>
       </c>
       <c r="B76" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8466,21 +8476,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8490,10 +8500,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437046</v>
+        <v>436761</v>
       </c>
       <c r="R76" t="n">
-        <v>7010396</v>
+        <v>7010448</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8526,11 +8536,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8557,10 +8562,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341002</v>
+        <v>132341124</v>
       </c>
       <c r="B77" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8568,21 +8573,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8592,10 +8597,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437060</v>
+        <v>436893</v>
       </c>
       <c r="R77" t="n">
-        <v>7010387</v>
+        <v>7010302</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8628,11 +8633,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9164,7 +9164,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341023</v>
+        <v>132341020</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437277</v>
+        <v>437311</v>
       </c>
       <c r="R83" t="n">
-        <v>7010440</v>
+        <v>7010307</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341020</v>
+        <v>132341004</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437311</v>
+        <v>437121</v>
       </c>
       <c r="R84" t="n">
-        <v>7010307</v>
+        <v>7010310</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9368,7 +9368,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341004</v>
+        <v>132341023</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -9403,10 +9403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437121</v>
+        <v>437277</v>
       </c>
       <c r="R85" t="n">
-        <v>7010310</v>
+        <v>7010440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9470,10 +9470,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341016</v>
+        <v>132341098</v>
       </c>
       <c r="B86" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436980</v>
+        <v>437162</v>
       </c>
       <c r="R86" t="n">
-        <v>7010332</v>
+        <v>7010098</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9541,11 +9541,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9572,7 +9567,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341010</v>
+        <v>132341016</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -9607,10 +9602,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437123</v>
+        <v>436980</v>
       </c>
       <c r="R87" t="n">
-        <v>7010418</v>
+        <v>7010332</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9647,7 +9642,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9674,7 +9669,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341019</v>
+        <v>132341010</v>
       </c>
       <c r="B88" t="n">
         <v>57953</v>
@@ -9709,10 +9704,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437276</v>
+        <v>437123</v>
       </c>
       <c r="R88" t="n">
-        <v>7010164</v>
+        <v>7010418</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9749,7 +9744,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9776,10 +9771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341098</v>
+        <v>132341019</v>
       </c>
       <c r="B89" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9787,21 +9782,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9811,10 +9806,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437162</v>
+        <v>437276</v>
       </c>
       <c r="R89" t="n">
-        <v>7010098</v>
+        <v>7010164</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9847,6 +9842,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -6119,7 +6119,7 @@
         <v>131882929</v>
       </c>
       <c r="B53" t="n">
-        <v>92281</v>
+        <v>92282</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>131882922</v>
       </c>
       <c r="B54" t="n">
-        <v>92281</v>
+        <v>92282</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6311,32 +6311,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341003</v>
+        <v>132341092</v>
       </c>
       <c r="B55" t="n">
-        <v>57953</v>
+        <v>92638</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437074</v>
+        <v>437194</v>
       </c>
       <c r="R55" t="n">
-        <v>7010349</v>
+        <v>7010065</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,17 +6384,13 @@
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6416,7 +6412,7 @@
         <v>132341014</v>
       </c>
       <c r="B56" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6515,32 +6511,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341092</v>
+        <v>132341003</v>
       </c>
       <c r="B57" t="n">
-        <v>92637</v>
+        <v>57954</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6550,10 +6546,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437194</v>
+        <v>437074</v>
       </c>
       <c r="R57" t="n">
-        <v>7010065</v>
+        <v>7010349</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6588,13 +6584,17 @@
           <t>2026-04-07</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>132341099</v>
       </c>
       <c r="B58" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>132341007</v>
       </c>
       <c r="B59" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341024</v>
+        <v>132341022</v>
       </c>
       <c r="B60" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437284</v>
+        <v>437263</v>
       </c>
       <c r="R60" t="n">
-        <v>7010437</v>
+        <v>7010455</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6917,7 +6917,7 @@
         <v>132341006</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7016,10 +7016,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341022</v>
+        <v>132341024</v>
       </c>
       <c r="B62" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437263</v>
+        <v>437284</v>
       </c>
       <c r="R62" t="n">
-        <v>7010455</v>
+        <v>7010437</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7121,7 +7121,7 @@
         <v>132341025</v>
       </c>
       <c r="B63" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>132341013</v>
       </c>
       <c r="B64" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>132341026</v>
       </c>
       <c r="B65" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7424,32 +7424,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132341012</v>
+        <v>132340934</v>
       </c>
       <c r="B66" t="n">
-        <v>57953</v>
+        <v>91873</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436992</v>
+        <v>437567</v>
       </c>
       <c r="R66" t="n">
-        <v>7010454</v>
+        <v>7010358</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,11 +7495,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7529,7 +7524,7 @@
         <v>132341017</v>
       </c>
       <c r="B67" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7628,32 +7623,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132340934</v>
+        <v>132341012</v>
       </c>
       <c r="B68" t="n">
-        <v>91872</v>
+        <v>57954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7663,10 +7658,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437567</v>
+        <v>436992</v>
       </c>
       <c r="R68" t="n">
-        <v>7010358</v>
+        <v>7010454</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,6 +7694,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7728,7 +7728,7 @@
         <v>132341009</v>
       </c>
       <c r="B69" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>132341008</v>
       </c>
       <c r="B70" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>132340950</v>
       </c>
       <c r="B71" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>132341093</v>
       </c>
       <c r="B72" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>132340999</v>
       </c>
       <c r="B73" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8261,10 +8261,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341002</v>
+        <v>132341123</v>
       </c>
       <c r="B74" t="n">
-        <v>57953</v>
+        <v>91906</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437060</v>
+        <v>436761</v>
       </c>
       <c r="R74" t="n">
-        <v>7010387</v>
+        <v>7010448</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,11 +8332,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8366,7 +8361,7 @@
         <v>132341000</v>
       </c>
       <c r="B75" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8465,10 +8460,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341123</v>
+        <v>132341002</v>
       </c>
       <c r="B76" t="n">
-        <v>91905</v>
+        <v>57954</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8476,21 +8471,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8500,10 +8495,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436761</v>
+        <v>437060</v>
       </c>
       <c r="R76" t="n">
-        <v>7010448</v>
+        <v>7010387</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8536,6 +8531,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8565,7 +8565,7 @@
         <v>132341124</v>
       </c>
       <c r="B77" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>132341021</v>
       </c>
       <c r="B78" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>132341015</v>
       </c>
       <c r="B79" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>132341122</v>
       </c>
       <c r="B80" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>132341001</v>
       </c>
       <c r="B81" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>132341011</v>
       </c>
       <c r="B82" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9164,10 +9164,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341020</v>
+        <v>132341023</v>
       </c>
       <c r="B83" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437311</v>
+        <v>437277</v>
       </c>
       <c r="R83" t="n">
-        <v>7010307</v>
+        <v>7010440</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9266,10 +9266,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341004</v>
+        <v>132341020</v>
       </c>
       <c r="B84" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437121</v>
+        <v>437311</v>
       </c>
       <c r="R84" t="n">
-        <v>7010310</v>
+        <v>7010307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9368,10 +9368,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341023</v>
+        <v>132341004</v>
       </c>
       <c r="B85" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437277</v>
+        <v>437121</v>
       </c>
       <c r="R85" t="n">
-        <v>7010440</v>
+        <v>7010310</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9473,7 +9473,7 @@
         <v>132341098</v>
       </c>
       <c r="B86" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>132341016</v>
       </c>
       <c r="B87" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9669,10 +9669,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341010</v>
+        <v>132341019</v>
       </c>
       <c r="B88" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9704,10 +9704,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437123</v>
+        <v>437276</v>
       </c>
       <c r="R88" t="n">
-        <v>7010418</v>
+        <v>7010164</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9771,10 +9771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341019</v>
+        <v>132341010</v>
       </c>
       <c r="B89" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9806,10 +9806,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437276</v>
+        <v>437123</v>
       </c>
       <c r="R89" t="n">
-        <v>7010164</v>
+        <v>7010418</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9876,7 +9876,7 @@
         <v>132341018</v>
       </c>
       <c r="B90" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>132796665</v>
       </c>
       <c r="B91" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89596063</v>
+        <v>132341092</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436981.1904009895</v>
+        <v>437194</v>
       </c>
       <c r="R2" t="n">
-        <v>7010361.935339754</v>
+        <v>7010065</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,61 +740,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89600474</v>
+        <v>131882932</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437010.0624254491</v>
+        <v>437149</v>
       </c>
       <c r="R3" t="n">
-        <v>7010383.025770075</v>
+        <v>7010477</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,69 +858,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89600477</v>
+        <v>131882917</v>
       </c>
       <c r="B4" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1588</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436842.8157022667</v>
+        <v>437024</v>
       </c>
       <c r="R4" t="n">
-        <v>7010470.20467878</v>
+        <v>7010309</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +935,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,69 +955,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89600484</v>
+        <v>131883755</v>
       </c>
       <c r="B5" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436842.8157022667</v>
+        <v>436954</v>
       </c>
       <c r="R5" t="n">
-        <v>7010470.20467878</v>
+        <v>7010327</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1032,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,69 +1062,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89600496</v>
+        <v>131883756</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436842.8157022667</v>
+        <v>436785</v>
       </c>
       <c r="R6" t="n">
-        <v>7010470.20467878</v>
+        <v>7010497</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1139,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,69 +1169,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89596062</v>
+        <v>131883758</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436898.0084983634</v>
+        <v>436781</v>
       </c>
       <c r="R7" t="n">
-        <v>7010405.065217823</v>
+        <v>7010439</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1246,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,69 +1276,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89600490</v>
+        <v>131882927</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436956.1862019072</v>
+        <v>437098</v>
       </c>
       <c r="R8" t="n">
-        <v>7010353.85233371</v>
+        <v>7010473</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,22 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,31 +1373,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89596056</v>
+        <v>131883773</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,37 +1396,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437018.1503997649</v>
+        <v>436865</v>
       </c>
       <c r="R9" t="n">
-        <v>7010427.078234297</v>
+        <v>7010395</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,22 +1450,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,66 +1480,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89600475</v>
+        <v>132341098</v>
       </c>
       <c r="B10" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436957.9572677925</v>
+        <v>437162</v>
       </c>
       <c r="R10" t="n">
-        <v>7010352.013189481</v>
+        <v>7010098</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,22 +1557,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,26 +1577,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131883760</v>
+        <v>132341099</v>
       </c>
       <c r="B11" t="n">
-        <v>83299</v>
+        <v>92245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,37 +1600,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436792</v>
+        <v>437567</v>
       </c>
       <c r="R11" t="n">
-        <v>7010489</v>
+        <v>7010357</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,22 +1654,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,22 +1674,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131883788</v>
+        <v>131883774</v>
       </c>
       <c r="B12" t="n">
-        <v>79319</v>
+        <v>91970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,21 +1697,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436776</v>
+        <v>437103</v>
       </c>
       <c r="R12" t="n">
-        <v>7010462</v>
+        <v>7010196</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1896,7 +1756,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1766,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131883780</v>
+        <v>132341122</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>91970</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,37 +1804,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437078</v>
+        <v>436784</v>
       </c>
       <c r="R13" t="n">
-        <v>7010262</v>
+        <v>7010502</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,22 +1858,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,22 +1878,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131882924</v>
+        <v>132341123</v>
       </c>
       <c r="B14" t="n">
-        <v>91898</v>
+        <v>91970</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,37 +1901,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436780</v>
+        <v>436761</v>
       </c>
       <c r="R14" t="n">
-        <v>7010451</v>
+        <v>7010448</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,12 +1955,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,22 +1975,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131883767</v>
+        <v>132341124</v>
       </c>
       <c r="B15" t="n">
-        <v>57949</v>
+        <v>91970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,42 +1998,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437078</v>
+        <v>436893</v>
       </c>
       <c r="R15" t="n">
-        <v>7010278</v>
+        <v>7010302</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,22 +2052,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,22 +2072,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131883755</v>
+        <v>89600474</v>
       </c>
       <c r="B16" t="n">
-        <v>78342</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,37 +2095,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436954</v>
+        <v>437010</v>
       </c>
       <c r="R16" t="n">
-        <v>7010327</v>
+        <v>7010383</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,22 +2149,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,22 +2169,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131883777</v>
+        <v>131882923</v>
       </c>
       <c r="B17" t="n">
-        <v>79319</v>
+        <v>91974</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,37 +2196,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437160</v>
+        <v>437082</v>
       </c>
       <c r="R17" t="n">
-        <v>7010163</v>
+        <v>7010188</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,19 +2253,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131883782</v>
+        <v>131882924</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>91974</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,37 +2293,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436983</v>
+        <v>436780</v>
       </c>
       <c r="R18" t="n">
-        <v>7010313</v>
+        <v>7010451</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2531,19 +2350,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131883759</v>
+        <v>131883761</v>
       </c>
       <c r="B19" t="n">
-        <v>83299</v>
+        <v>91974</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436787</v>
+        <v>437164</v>
       </c>
       <c r="R19" t="n">
-        <v>7010440</v>
+        <v>7010163</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2640,7 +2449,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2459,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131883766</v>
+        <v>131883762</v>
       </c>
       <c r="B20" t="n">
-        <v>57949</v>
+        <v>91974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,39 +2497,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437079</v>
+        <v>436892</v>
       </c>
       <c r="R20" t="n">
-        <v>7010238</v>
+        <v>7010367</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2752,7 +2556,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,7 +2566,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,10 +2593,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131883786</v>
+        <v>131883764</v>
       </c>
       <c r="B21" t="n">
-        <v>79319</v>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,21 +2604,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2824,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436857</v>
+        <v>436864</v>
       </c>
       <c r="R21" t="n">
-        <v>7010396</v>
+        <v>7010391</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2859,7 +2663,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2673,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2896,32 +2700,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131882928</v>
+        <v>131882926</v>
       </c>
       <c r="B22" t="n">
-        <v>97971</v>
+        <v>92406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2931,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437191</v>
+        <v>437234</v>
       </c>
       <c r="R22" t="n">
-        <v>7010182</v>
+        <v>7010154</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2993,53 +2797,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131883769</v>
+        <v>89600477</v>
       </c>
       <c r="B23" t="n">
-        <v>57137</v>
+        <v>92097</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437337</v>
+        <v>436843</v>
       </c>
       <c r="R23" t="n">
-        <v>7010352</v>
+        <v>7010470</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3063,22 +2862,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,60 +2882,64 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131883761</v>
+        <v>131882922</v>
       </c>
       <c r="B24" t="n">
-        <v>91898</v>
+        <v>92318</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437164</v>
+        <v>437158</v>
       </c>
       <c r="R24" t="n">
-        <v>7010163</v>
+        <v>7010174</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,19 +2966,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,48 +2995,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131883789</v>
+        <v>131882929</v>
       </c>
       <c r="B25" t="n">
-        <v>79319</v>
+        <v>92318</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436780</v>
+        <v>436862</v>
       </c>
       <c r="R25" t="n">
-        <v>7010490</v>
+        <v>7010393</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3280,27 +3063,18 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3319,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131883775</v>
+        <v>89600496</v>
       </c>
       <c r="B26" t="n">
-        <v>79319</v>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3330,37 +3104,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437320</v>
+        <v>436843</v>
       </c>
       <c r="R26" t="n">
-        <v>7010358</v>
+        <v>7010470</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3384,22 +3158,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,60 +3178,64 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131883776</v>
+        <v>89600475</v>
       </c>
       <c r="B27" t="n">
-        <v>79319</v>
+        <v>92632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437286</v>
+        <v>436958</v>
       </c>
       <c r="R27" t="n">
-        <v>7010179</v>
+        <v>7010352</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3491,22 +3259,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,60 +3279,64 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131882931</v>
+        <v>132340950</v>
       </c>
       <c r="B28" t="n">
-        <v>79319</v>
+        <v>92199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436952</v>
+        <v>436918</v>
       </c>
       <c r="R28" t="n">
-        <v>7010316</v>
+        <v>7010313</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3598,12 +3360,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3618,60 +3380,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131883784</v>
+        <v>132340934</v>
       </c>
       <c r="B29" t="n">
-        <v>79319</v>
+        <v>91937</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436930</v>
+        <v>437567</v>
       </c>
       <c r="R29" t="n">
-        <v>7010353</v>
+        <v>7010358</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3695,22 +3457,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3725,65 +3477,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131883765</v>
+        <v>89596062</v>
       </c>
       <c r="B30" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437208</v>
+        <v>436898</v>
       </c>
       <c r="R30" t="n">
-        <v>7010169</v>
+        <v>7010405</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3807,22 +3554,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3837,60 +3574,64 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131882927</v>
+        <v>89596063</v>
       </c>
       <c r="B31" t="n">
-        <v>92197</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437098</v>
+        <v>436981</v>
       </c>
       <c r="R31" t="n">
-        <v>7010473</v>
+        <v>7010362</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3914,12 +3655,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3934,44 +3675,48 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131882917</v>
+        <v>131882930</v>
       </c>
       <c r="B32" t="n">
-        <v>78342</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3981,10 +3726,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437024</v>
+        <v>437227</v>
       </c>
       <c r="R32" t="n">
-        <v>7010309</v>
+        <v>7010158</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4043,14 +3788,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131883787</v>
+        <v>131882931</v>
       </c>
       <c r="B33" t="n">
-        <v>79319</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4074,17 +3819,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436824</v>
+        <v>436952</v>
       </c>
       <c r="R33" t="n">
-        <v>7010448</v>
+        <v>7010316</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4111,19 +3856,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4150,14 +3885,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131883778</v>
+        <v>131883775</v>
       </c>
       <c r="B34" t="n">
-        <v>79319</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4185,10 +3920,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>437111</v>
+        <v>437320</v>
       </c>
       <c r="R34" t="n">
-        <v>7010195</v>
+        <v>7010358</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4220,7 +3955,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4230,7 +3965,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4257,14 +3992,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131883781</v>
+        <v>131883776</v>
       </c>
       <c r="B35" t="n">
-        <v>79319</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4292,10 +4027,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437028</v>
+        <v>437286</v>
       </c>
       <c r="R35" t="n">
-        <v>7010314</v>
+        <v>7010179</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4327,7 +4062,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4337,7 +4072,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4364,32 +4099,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131883758</v>
+        <v>131883777</v>
       </c>
       <c r="B36" t="n">
-        <v>78342</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4399,10 +4134,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436781</v>
+        <v>437160</v>
       </c>
       <c r="R36" t="n">
-        <v>7010439</v>
+        <v>7010163</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4434,7 +4169,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4444,7 +4179,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4471,14 +4206,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131883785</v>
+        <v>131883778</v>
       </c>
       <c r="B37" t="n">
-        <v>79319</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4506,10 +4241,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436881</v>
+        <v>437111</v>
       </c>
       <c r="R37" t="n">
-        <v>7010368</v>
+        <v>7010195</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4541,7 +4276,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4551,7 +4286,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4578,48 +4313,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131882919</v>
+        <v>131883779</v>
       </c>
       <c r="B38" t="n">
-        <v>83299</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436779</v>
+        <v>437081</v>
       </c>
       <c r="R38" t="n">
-        <v>7010478</v>
+        <v>7010232</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4646,9 +4381,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4675,14 +4420,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131883779</v>
+        <v>131883780</v>
       </c>
       <c r="B39" t="n">
-        <v>79319</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4710,10 +4455,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437081</v>
+        <v>437078</v>
       </c>
       <c r="R39" t="n">
-        <v>7010232</v>
+        <v>7010262</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4745,7 +4490,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4755,7 +4500,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4782,10 +4527,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131882926</v>
+        <v>131883781</v>
       </c>
       <c r="B40" t="n">
-        <v>92358</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4793,37 +4538,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437234</v>
+        <v>437028</v>
       </c>
       <c r="R40" t="n">
-        <v>7010154</v>
+        <v>7010314</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4850,9 +4595,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4879,32 +4634,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131883756</v>
+        <v>131883782</v>
       </c>
       <c r="B41" t="n">
-        <v>78342</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4914,10 +4669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436785</v>
+        <v>436983</v>
       </c>
       <c r="R41" t="n">
-        <v>7010497</v>
+        <v>7010313</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4949,7 +4704,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4959,7 +4714,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,50 +4741,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131883768</v>
+        <v>131883784</v>
       </c>
       <c r="B42" t="n">
-        <v>57949</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437044</v>
+        <v>436930</v>
       </c>
       <c r="R42" t="n">
-        <v>7010321</v>
+        <v>7010353</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5061,7 +4811,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5071,7 +4821,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,48 +4848,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131882932</v>
+        <v>131883785</v>
       </c>
       <c r="B43" t="n">
-        <v>83291</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437149</v>
+        <v>436881</v>
       </c>
       <c r="R43" t="n">
-        <v>7010477</v>
+        <v>7010368</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5166,9 +4916,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,48 +4955,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131882920</v>
+        <v>131883786</v>
       </c>
       <c r="B44" t="n">
-        <v>79938</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437363</v>
+        <v>436857</v>
       </c>
       <c r="R44" t="n">
-        <v>7010325</v>
+        <v>7010396</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5263,9 +5023,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5292,32 +5062,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131883774</v>
+        <v>131883787</v>
       </c>
       <c r="B45" t="n">
-        <v>91894</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5327,10 +5097,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437103</v>
+        <v>436824</v>
       </c>
       <c r="R45" t="n">
-        <v>7010196</v>
+        <v>7010448</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5362,7 +5132,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5372,7 +5142,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5399,48 +5169,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131882923</v>
+        <v>131883788</v>
       </c>
       <c r="B46" t="n">
-        <v>91898</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>437082</v>
+        <v>436776</v>
       </c>
       <c r="R46" t="n">
-        <v>7010188</v>
+        <v>7010462</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5467,9 +5237,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5496,14 +5276,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131882930</v>
+        <v>131883789</v>
       </c>
       <c r="B47" t="n">
-        <v>79319</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5527,17 +5307,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437227</v>
+        <v>436780</v>
       </c>
       <c r="R47" t="n">
-        <v>7010158</v>
+        <v>7010490</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5564,9 +5344,19 @@
           <t>2026-03-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5593,10 +5383,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131883773</v>
+        <v>131882919</v>
       </c>
       <c r="B48" t="n">
-        <v>92197</v>
+        <v>83358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,37 +5394,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Baksjöbodarna  Öster, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436865</v>
+        <v>436779</v>
       </c>
       <c r="R48" t="n">
-        <v>7010395</v>
+        <v>7010478</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5661,19 +5451,9 @@
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5700,10 +5480,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131883762</v>
+        <v>131883759</v>
       </c>
       <c r="B49" t="n">
-        <v>91898</v>
+        <v>83358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5711,21 +5491,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5735,10 +5515,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436892</v>
+        <v>436787</v>
       </c>
       <c r="R49" t="n">
-        <v>7010367</v>
+        <v>7010440</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5770,7 +5550,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5780,7 +5560,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5807,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131883764</v>
+        <v>131883760</v>
       </c>
       <c r="B50" t="n">
-        <v>91898</v>
+        <v>83358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5818,21 +5598,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5842,10 +5622,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436864</v>
+        <v>436792</v>
       </c>
       <c r="R50" t="n">
-        <v>7010391</v>
+        <v>7010489</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5877,7 +5657,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5887,7 +5667,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5914,10 +5694,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131882925</v>
+        <v>131882920</v>
       </c>
       <c r="B51" t="n">
-        <v>57949</v>
+        <v>79992</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5925,42 +5705,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437206</v>
+        <v>437363</v>
       </c>
       <c r="R51" t="n">
-        <v>7010436</v>
+        <v>7010325</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6019,48 +5791,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131882921</v>
+        <v>89600484</v>
       </c>
       <c r="B52" t="n">
-        <v>79909</v>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437362</v>
+        <v>436843</v>
       </c>
       <c r="R52" t="n">
-        <v>7010336</v>
+        <v>7010470</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6084,12 +5856,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6104,60 +5876,80 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131882929</v>
+        <v>132341093</v>
       </c>
       <c r="B53" t="n">
-        <v>92285</v>
+        <v>57972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Baksjöbodarna Östra, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436862</v>
+        <v>437170</v>
       </c>
       <c r="R53" t="n">
-        <v>7010393</v>
+        <v>7010069</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6181,12 +5973,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6195,64 +5987,71 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131882922</v>
+        <v>131882925</v>
       </c>
       <c r="B54" t="n">
-        <v>92285</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437158</v>
+        <v>437206</v>
       </c>
       <c r="R54" t="n">
-        <v>7010174</v>
+        <v>7010436</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6311,48 +6110,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132341092</v>
+        <v>131883765</v>
       </c>
       <c r="B55" t="n">
-        <v>92644</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437194</v>
+        <v>437208</v>
       </c>
       <c r="R55" t="n">
-        <v>7010065</v>
+        <v>7010169</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6376,43 +6180,52 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132341003</v>
+        <v>131883766</v>
       </c>
       <c r="B56" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6438,19 +6251,24 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437074</v>
+        <v>437079</v>
       </c>
       <c r="R56" t="n">
-        <v>7010349</v>
+        <v>7010238</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6474,17 +6292,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6499,22 +6322,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132341014</v>
+        <v>131883767</v>
       </c>
       <c r="B57" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6540,19 +6363,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436800</v>
+        <v>437078</v>
       </c>
       <c r="R57" t="n">
-        <v>7010351</v>
+        <v>7010278</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6576,17 +6404,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6601,22 +6434,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132341099</v>
+        <v>131883768</v>
       </c>
       <c r="B58" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6624,37 +6457,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437567</v>
+        <v>437044</v>
       </c>
       <c r="R58" t="n">
-        <v>7010357</v>
+        <v>7010321</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6678,12 +6516,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6698,22 +6546,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132341007</v>
+        <v>132340999</v>
       </c>
       <c r="B59" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6738,17 +6586,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437143</v>
+        <v>436960</v>
       </c>
       <c r="R59" t="n">
-        <v>7010271</v>
+        <v>7010414</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6785,7 +6653,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande hanne</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6812,10 +6680,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132341024</v>
+        <v>132341000</v>
       </c>
       <c r="B60" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6847,10 +6715,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437284</v>
+        <v>437046</v>
       </c>
       <c r="R60" t="n">
-        <v>7010437</v>
+        <v>7010396</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6887,7 +6755,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6914,10 +6782,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132341006</v>
+        <v>132341001</v>
       </c>
       <c r="B61" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6949,10 +6817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437113</v>
+        <v>437047</v>
       </c>
       <c r="R61" t="n">
-        <v>7010291</v>
+        <v>7010396</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7016,10 +6884,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132341022</v>
+        <v>132341002</v>
       </c>
       <c r="B62" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7051,10 +6919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437263</v>
+        <v>437060</v>
       </c>
       <c r="R62" t="n">
-        <v>7010455</v>
+        <v>7010387</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7091,7 +6959,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7118,10 +6986,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132341025</v>
+        <v>132341003</v>
       </c>
       <c r="B63" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7153,10 +7021,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437286</v>
+        <v>437074</v>
       </c>
       <c r="R63" t="n">
-        <v>7010436</v>
+        <v>7010349</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7193,7 +7061,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7220,10 +7088,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132341013</v>
+        <v>132341004</v>
       </c>
       <c r="B64" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7255,10 +7123,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436675</v>
+        <v>437121</v>
       </c>
       <c r="R64" t="n">
-        <v>7010368</v>
+        <v>7010310</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7295,7 +7163,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7322,10 +7190,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132341026</v>
+        <v>132341006</v>
       </c>
       <c r="B65" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7357,10 +7225,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437430</v>
+        <v>437113</v>
       </c>
       <c r="R65" t="n">
-        <v>7010447</v>
+        <v>7010291</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7397,7 +7265,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7424,32 +7292,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132340934</v>
+        <v>132341007</v>
       </c>
       <c r="B66" t="n">
-        <v>91879</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7459,10 +7327,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437567</v>
+        <v>437143</v>
       </c>
       <c r="R66" t="n">
-        <v>7010358</v>
+        <v>7010271</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,6 +7363,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7521,10 +7394,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132341012</v>
+        <v>132341008</v>
       </c>
       <c r="B67" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7556,10 +7429,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436992</v>
+        <v>437222</v>
       </c>
       <c r="R67" t="n">
-        <v>7010454</v>
+        <v>7010260</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7596,7 +7469,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7623,10 +7496,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132341017</v>
+        <v>132341009</v>
       </c>
       <c r="B68" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7658,10 +7531,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436985</v>
+        <v>437127</v>
       </c>
       <c r="R68" t="n">
-        <v>7010332</v>
+        <v>7010372</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7698,7 +7571,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7725,10 +7598,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132341009</v>
+        <v>132341010</v>
       </c>
       <c r="B69" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7760,10 +7633,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437127</v>
+        <v>437123</v>
       </c>
       <c r="R69" t="n">
-        <v>7010372</v>
+        <v>7010418</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7800,7 +7673,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7827,10 +7700,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132341008</v>
+        <v>132341011</v>
       </c>
       <c r="B70" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7862,10 +7735,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437222</v>
+        <v>437059</v>
       </c>
       <c r="R70" t="n">
-        <v>7010260</v>
+        <v>7010469</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7929,32 +7802,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132340950</v>
+        <v>132341012</v>
       </c>
       <c r="B71" t="n">
-        <v>92639</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7964,10 +7837,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436918</v>
+        <v>436992</v>
       </c>
       <c r="R71" t="n">
-        <v>7010313</v>
+        <v>7010454</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8000,6 +7873,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8026,10 +7904,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132341093</v>
+        <v>132341013</v>
       </c>
       <c r="B72" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8037,16 +7915,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8054,33 +7932,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437170</v>
+        <v>436675</v>
       </c>
       <c r="R72" t="n">
-        <v>7010069</v>
+        <v>7010368</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8113,6 +7975,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8139,7 +8006,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132340999</v>
+        <v>132341014</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8167,37 +8034,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436960</v>
+        <v>436800</v>
       </c>
       <c r="R73" t="n">
-        <v>7010414</v>
+        <v>7010351</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8234,7 +8081,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Födosökande hanne</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8261,10 +8108,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132341123</v>
+        <v>132341015</v>
       </c>
       <c r="B74" t="n">
-        <v>91912</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8272,21 +8119,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8143,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436761</v>
+        <v>436933</v>
       </c>
       <c r="R74" t="n">
-        <v>7010448</v>
+        <v>7010291</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,6 +8179,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8358,10 +8210,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132341124</v>
+        <v>132341016</v>
       </c>
       <c r="B75" t="n">
-        <v>91912</v>
+        <v>57975</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8369,21 +8221,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8393,10 +8245,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436893</v>
+        <v>436980</v>
       </c>
       <c r="R75" t="n">
-        <v>7010302</v>
+        <v>7010332</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,6 +8281,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8455,10 +8312,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132341002</v>
+        <v>132341017</v>
       </c>
       <c r="B76" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8490,10 +8347,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437060</v>
+        <v>436985</v>
       </c>
       <c r="R76" t="n">
-        <v>7010387</v>
+        <v>7010332</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8530,7 +8387,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8557,10 +8414,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132341000</v>
+        <v>132341018</v>
       </c>
       <c r="B77" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8592,10 +8449,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437046</v>
+        <v>437148</v>
       </c>
       <c r="R77" t="n">
-        <v>7010396</v>
+        <v>7010084</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8632,7 +8489,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8659,10 +8516,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132341021</v>
+        <v>132341019</v>
       </c>
       <c r="B78" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8694,10 +8551,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437255</v>
+        <v>437276</v>
       </c>
       <c r="R78" t="n">
-        <v>7010456</v>
+        <v>7010164</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8761,10 +8618,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132341015</v>
+        <v>132341020</v>
       </c>
       <c r="B79" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8796,10 +8653,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436933</v>
+        <v>437311</v>
       </c>
       <c r="R79" t="n">
-        <v>7010291</v>
+        <v>7010307</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8836,7 +8693,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8863,10 +8720,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132341122</v>
+        <v>132341021</v>
       </c>
       <c r="B80" t="n">
-        <v>91912</v>
+        <v>57975</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8874,21 +8731,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8898,10 +8755,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436784</v>
+        <v>437255</v>
       </c>
       <c r="R80" t="n">
-        <v>7010502</v>
+        <v>7010456</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8934,6 +8791,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8960,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132341001</v>
+        <v>132341022</v>
       </c>
       <c r="B81" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8995,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437047</v>
+        <v>437263</v>
       </c>
       <c r="R81" t="n">
-        <v>7010396</v>
+        <v>7010455</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9062,10 +8924,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132341011</v>
+        <v>132341023</v>
       </c>
       <c r="B82" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9097,10 +8959,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437059</v>
+        <v>437277</v>
       </c>
       <c r="R82" t="n">
-        <v>7010469</v>
+        <v>7010440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9164,10 +9026,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132341020</v>
+        <v>132341024</v>
       </c>
       <c r="B83" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9199,10 +9061,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437311</v>
+        <v>437284</v>
       </c>
       <c r="R83" t="n">
-        <v>7010307</v>
+        <v>7010437</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9266,10 +9128,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132341004</v>
+        <v>132341025</v>
       </c>
       <c r="B84" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9301,10 +9163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437121</v>
+        <v>437286</v>
       </c>
       <c r="R84" t="n">
-        <v>7010310</v>
+        <v>7010436</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9368,10 +9230,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132341023</v>
+        <v>132341026</v>
       </c>
       <c r="B85" t="n">
-        <v>57957</v>
+        <v>57975</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9403,10 +9265,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437277</v>
+        <v>437430</v>
       </c>
       <c r="R85" t="n">
-        <v>7010440</v>
+        <v>7010447</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9443,7 +9305,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9470,10 +9332,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132341098</v>
+        <v>132796665</v>
       </c>
       <c r="B86" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9481,34 +9343,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437162</v>
+        <v>437176</v>
       </c>
       <c r="R86" t="n">
-        <v>7010098</v>
+        <v>7010505</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9535,12 +9397,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9555,60 +9427,65 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132341016</v>
+        <v>131883769</v>
       </c>
       <c r="B87" t="n">
-        <v>57957</v>
+        <v>57162</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöbodarna  Öster, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436980</v>
+        <v>437337</v>
       </c>
       <c r="R87" t="n">
-        <v>7010332</v>
+        <v>7010352</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9632,17 +9509,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9657,60 +9539,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132341010</v>
+        <v>131882928</v>
       </c>
       <c r="B88" t="n">
-        <v>57957</v>
+        <v>98060</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>437123</v>
+        <v>437191</v>
       </c>
       <c r="R88" t="n">
-        <v>7010418</v>
+        <v>7010182</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9734,17 +9616,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9759,57 +9636,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132341019</v>
+        <v>89600490</v>
       </c>
       <c r="B89" t="n">
-        <v>57957</v>
+        <v>99140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>437276</v>
+        <v>436956</v>
       </c>
       <c r="R89" t="n">
-        <v>7010164</v>
+        <v>7010354</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9836,17 +9713,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9861,22 +9733,26 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132341018</v>
+        <v>131882921</v>
       </c>
       <c r="B90" t="n">
-        <v>57957</v>
+        <v>79963</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,37 +9760,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöbodarna Östra, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>437148</v>
+        <v>437362</v>
       </c>
       <c r="R90" t="n">
-        <v>7010084</v>
+        <v>7010336</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9938,17 +9814,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9963,122 +9834,15 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>132796665</v>
-      </c>
-      <c r="B91" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>437176</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7010505</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Mattmar</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Matilda Pettersson</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Matilda Pettersson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10605-2026 artfynd.xlsx
+++ b/artfynd/A 10605-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882932</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882917</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883755</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883756</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883758</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882927</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,6 +1529,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883773</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341098</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341099</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883774</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341122</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1984,6 +2049,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341123</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2081,6 +2151,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341124</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2182,6 +2257,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600474</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2279,6 +2359,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882923</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882924</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2483,6 +2573,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883761</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2590,6 +2685,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883762</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883764</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2794,6 +2899,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882926</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2895,6 +3005,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600477</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2992,6 +3107,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882922</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3090,6 +3210,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882929</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3191,6 +3316,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600496</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3292,6 +3422,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600475</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3389,6 +3524,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340950</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3486,6 +3626,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340934</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3587,6 +3732,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596062</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3688,6 +3838,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596063</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3785,6 +3940,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882930</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3882,6 +4042,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882931</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3989,6 +4154,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883775</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4096,6 +4266,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883776</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4203,6 +4378,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883777</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4310,6 +4490,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883778</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4417,6 +4602,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883779</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4524,6 +4714,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883780</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4631,6 +4826,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883781</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4738,6 +4938,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883782</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4845,6 +5050,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883784</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4952,6 +5162,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883785</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5059,6 +5274,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883786</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5166,6 +5386,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883787</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5273,6 +5498,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883788</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5380,6 +5610,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883789</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5477,6 +5712,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882919</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5584,6 +5824,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883759</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5691,6 +5936,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883760</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5788,6 +6038,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882920</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5889,6 +6144,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600484</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6002,6 +6262,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341093</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6107,6 +6372,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882925</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6219,6 +6489,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883765</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6331,6 +6606,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883766</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6443,6 +6723,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883767</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6555,6 +6840,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883768</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6677,6 +6967,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340999</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6779,6 +7074,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341000</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6881,6 +7181,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341001</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6983,6 +7288,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341002</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7085,6 +7395,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341003</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7187,6 +7502,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341004</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7289,6 +7609,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341006</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7391,6 +7716,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341007</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7493,6 +7823,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341008</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7595,6 +7930,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341009</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7697,6 +8037,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341010</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7799,6 +8144,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341011</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7901,6 +8251,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341012</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8003,6 +8358,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341013</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8105,6 +8465,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341014</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8207,6 +8572,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341015</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8309,6 +8679,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341016</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8411,6 +8786,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341017</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8513,6 +8893,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341018</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8615,6 +9000,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341019</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8717,6 +9107,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341020</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8819,6 +9214,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341021</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8921,6 +9321,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341022</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9023,6 +9428,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341023</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9125,6 +9535,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341024</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9227,6 +9642,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341025</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9329,6 +9749,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341026</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9436,6 +9861,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132796665</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9548,6 +9978,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883769</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9645,6 +10080,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882928</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9746,6 +10186,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600490</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9843,8 +10288,104 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>